--- a/docs/功能归属表.xlsx
+++ b/docs/功能归属表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaizhou/SynologyDrive/works/fxn-wms/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{021A3CB8-5265-1949-A2FE-17D021B2CA5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD03C9D9-E451-EF4A-973A-E5DE49DEE5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="21240" xr2:uid="{83DC34A4-855E-F341-94CD-123EDADA1840}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="153">
   <si>
     <t>功能模块</t>
   </si>
@@ -399,6 +399,106 @@
   </si>
   <si>
     <t>✅ 接收任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QMS 职责</t>
+  </si>
+  <si>
+    <t>PDA 职责</t>
+  </si>
+  <si>
+    <t>物料分类识别</t>
+  </si>
+  <si>
+    <t>✅ 读取物料主数据</t>
+  </si>
+  <si>
+    <t>路由决策</t>
+  </si>
+  <si>
+    <t>✅ 根据物料类型决策路径</t>
+  </si>
+  <si>
+    <t>库位分配</t>
+  </si>
+  <si>
+    <t>✅ 自动分配目标库位</t>
+  </si>
+  <si>
+    <t>码头绑定</t>
+  </si>
+  <si>
+    <t>✅ 记录绑定关系</t>
+  </si>
+  <si>
+    <t>✅ 扫码绑定</t>
+  </si>
+  <si>
+    <t>运输调度</t>
+  </si>
+  <si>
+    <t>✅ 调用 RCS API</t>
+  </si>
+  <si>
+    <t>IQC 取样</t>
+  </si>
+  <si>
+    <t>✅ 生成取样任务</t>
+  </si>
+  <si>
+    <t>✅ 接收取样请求</t>
+  </si>
+  <si>
+    <t>✅ 扫码取样</t>
+  </si>
+  <si>
+    <t>检验结果处理</t>
+  </si>
+  <si>
+    <t>✅ 接收并处理检验结果</t>
+  </si>
+  <si>
+    <t>✅ 推送检验结果</t>
+  </si>
+  <si>
+    <t>入库确认</t>
+  </si>
+  <si>
+    <t>✅ 更新库存状态</t>
+  </si>
+  <si>
+    <t>✅ 扫码确认</t>
+  </si>
+  <si>
+    <t>六合一绑定</t>
+  </si>
+  <si>
+    <t>手动扫描送货</t>
+  </si>
+  <si>
+    <t>✅ 生成运输任务</t>
+  </si>
+  <si>
+    <t>✅ 扫码操作</t>
+  </si>
+  <si>
+    <t>库存管理</t>
+  </si>
+  <si>
+    <t>✅ 维护库存数据</t>
+  </si>
+  <si>
+    <t>✅ 人工操作</t>
+  </si>
+  <si>
+    <t>SAP 同步</t>
+  </si>
+  <si>
+    <t>✅ 批量同步库存数据</t>
+  </si>
+  <si>
+    <t>特殊物料入库</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -845,7 +945,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945DC6DF-BE66-CF42-AA2D-016BA392A074}">
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F70"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="22" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="20" style="2" bestFit="1" customWidth="1"/>
@@ -1852,6 +1952,256 @@
         <v>8</v>
       </c>
     </row>
+    <row r="56" spans="1:6" ht="22" customHeight="1">
+      <c r="A56" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="B56" s="5"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="5"/>
+      <c r="E56" s="5"/>
+    </row>
+    <row r="57" spans="1:6" ht="22" customHeight="1">
+      <c r="A57" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="22" customHeight="1">
+      <c r="A58" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="B58" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="22" customHeight="1">
+      <c r="A59" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="B59" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="22" customHeight="1">
+      <c r="A60" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="B60" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E60" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F60" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="22" customHeight="1">
+      <c r="A61" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="B61" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" ht="22" customHeight="1">
+      <c r="A62" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="B62" s="5" t="s">
+        <v>132</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E62" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F62" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" ht="22" customHeight="1">
+      <c r="A63" s="5" t="s">
+        <v>133</v>
+      </c>
+      <c r="B63" s="5" t="s">
+        <v>134</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E63" s="5" t="s">
+        <v>135</v>
+      </c>
+      <c r="F63" s="5" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="22" customHeight="1">
+      <c r="A64" s="5" t="s">
+        <v>137</v>
+      </c>
+      <c r="B64" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>139</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" ht="22" customHeight="1">
+      <c r="A65" s="5" t="s">
+        <v>140</v>
+      </c>
+      <c r="B65" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="5" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="22" customHeight="1">
+      <c r="A66" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="B66" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="5" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="22" customHeight="1">
+      <c r="A67" s="5" t="s">
+        <v>144</v>
+      </c>
+      <c r="B67" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E67" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="5" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="22" customHeight="1">
+      <c r="A68" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="B68" s="5" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="22" customHeight="1">
+      <c r="A69" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B69" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="E69" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F69" s="5" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="22" customHeight="1">
+      <c r="A70" s="5" t="s">
+        <v>150</v>
+      </c>
+      <c r="B70" s="5" t="s">
+        <v>151</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="5" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/功能归属表.xlsx
+++ b/docs/功能归属表.xlsx
@@ -8,13 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaizhou/SynologyDrive/works/fxn-wms/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DD03C9D9-E451-EF4A-973A-E5DE49DEE5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82639C7B-2541-1C47-B75A-E4B6B806D844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="800" windowWidth="36000" windowHeight="21240" xr2:uid="{83DC34A4-855E-F341-94CD-123EDADA1840}"/>
+    <workbookView xWindow="700" yWindow="800" windowWidth="32580" windowHeight="18720" activeTab="1" xr2:uid="{83DC34A4-855E-F341-94CD-123EDADA1840}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$I$182</definedName>
+  </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="369" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="518">
   <si>
     <t>功能模块</t>
   </si>
@@ -499,6 +503,1112 @@
   </si>
   <si>
     <t>特殊物料入库</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到货登记</t>
+  </si>
+  <si>
+    <t>✅ PDA登记、清单导入</t>
+  </si>
+  <si>
+    <t>清单导入</t>
+  </si>
+  <si>
+    <t>✅ Excel导入、SAP对接</t>
+  </si>
+  <si>
+    <t>GRN单据接入</t>
+  </si>
+  <si>
+    <t>✅ SAP对接、主账管理</t>
+  </si>
+  <si>
+    <t>栈板号生成</t>
+  </si>
+  <si>
+    <t>✅ 号段管理、规则维护</t>
+  </si>
+  <si>
+    <t>标签渲染打印</t>
+  </si>
+  <si>
+    <t>✅ ZPL渲染、打印管理</t>
+  </si>
+  <si>
+    <t>PDA绑定</t>
+  </si>
+  <si>
+    <t>✅ 绑定校验、数据汇总</t>
+  </si>
+  <si>
+    <t>搬运任务创建</t>
+  </si>
+  <si>
+    <t>✅ 任务生成、RCS调度</t>
+  </si>
+  <si>
+    <t>✅ AGV执行</t>
+  </si>
+  <si>
+    <t>码头区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>QMS抽检策略查询</t>
+  </si>
+  <si>
+    <t>✅ GRN推送、策略接收</t>
+  </si>
+  <si>
+    <t>送检优先级调整</t>
+  </si>
+  <si>
+    <t>✅ 优先级管理、审计</t>
+  </si>
+  <si>
+    <t>IQC取样记录</t>
+  </si>
+  <si>
+    <t>✅ PDA扫描、数据记录</t>
+  </si>
+  <si>
+    <t>IQC归还记录</t>
+  </si>
+  <si>
+    <t>✅ PDA扫描、校验匹配</t>
+  </si>
+  <si>
+    <t>检验结果获取</t>
+  </si>
+  <si>
+    <t>✅ QMS查询、结果处理</t>
+  </si>
+  <si>
+    <t>✅ 决策引擎、任务生成</t>
+  </si>
+  <si>
+    <t>复判结果处理</t>
+  </si>
+  <si>
+    <t>✅ QMS查询、路由生成</t>
+  </si>
+  <si>
+    <t>拆板作业</t>
+  </si>
+  <si>
+    <t>✅ PDA操作、数据更新</t>
+  </si>
+  <si>
+    <t>暂存区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>搬运任务执行</t>
+  </si>
+  <si>
+    <t>IQC送检任务创建</t>
+  </si>
+  <si>
+    <t>IQC送检搬运执行</t>
+  </si>
+  <si>
+    <t>路由搬运执行</t>
+  </si>
+  <si>
+    <t>复判搬运执行</t>
+  </si>
+  <si>
+    <t>Epic</t>
+  </si>
+  <si>
+    <t>用户故事</t>
+  </si>
+  <si>
+    <t>故事点</t>
+  </si>
+  <si>
+    <t>优先级</t>
+  </si>
+  <si>
+    <t>依赖</t>
+  </si>
+  <si>
+    <t>E1: 到货登记与清单管理</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>无</t>
+  </si>
+  <si>
+    <t>US-E1-01: 到货信息登记</t>
+  </si>
+  <si>
+    <t>US-E1-02: 到货清单导入</t>
+  </si>
+  <si>
+    <t>US-E1-03: SAP GRN 单号请求</t>
+  </si>
+  <si>
+    <t>US-E1-04: 到货列表查询</t>
+  </si>
+  <si>
+    <t>E2: 单据数据同步</t>
+  </si>
+  <si>
+    <t>E1</t>
+  </si>
+  <si>
+    <t>US-E2-01: WMS 推送 GRN 副本</t>
+  </si>
+  <si>
+    <t>US-E2-03: GRN 同步监控</t>
+  </si>
+  <si>
+    <t>E2-01</t>
+  </si>
+  <si>
+    <t>E3: 栈板标签生成与打印</t>
+  </si>
+  <si>
+    <t>US-E3-01: 栈板号生成服务</t>
+  </si>
+  <si>
+    <t>US-E3-02: 栈板准备界面</t>
+  </si>
+  <si>
+    <t>E3-01</t>
+  </si>
+  <si>
+    <t>US-E3-03: ZPL 标签模板渲染</t>
+  </si>
+  <si>
+    <t>US-E3-04: 直接打印服务</t>
+  </si>
+  <si>
+    <t>E3-03</t>
+  </si>
+  <si>
+    <t>US-E3-05: 自动打印服务</t>
+  </si>
+  <si>
+    <t>US-E3-06: 打印失败处理</t>
+  </si>
+  <si>
+    <t>E3-04</t>
+  </si>
+  <si>
+    <t>E4: PDA 绑定操作</t>
+  </si>
+  <si>
+    <t>E3</t>
+  </si>
+  <si>
+    <t>US-E4-01: PDA 地码扫描与校验</t>
+  </si>
+  <si>
+    <t>US-E4-02: PDA 栈板号扫描与校验</t>
+  </si>
+  <si>
+    <t>E4-01</t>
+  </si>
+  <si>
+    <t>US-E4-03: PDA 箱条码扫描与 GRN 绑定</t>
+  </si>
+  <si>
+    <t>E4-02</t>
+  </si>
+  <si>
+    <t>US-E4-04: 绑定数量校验</t>
+  </si>
+  <si>
+    <t>E4-03</t>
+  </si>
+  <si>
+    <t>US-E4-05: 混托物料类型兼容性校验</t>
+  </si>
+  <si>
+    <t>US-E4-06: 栈板绑定完成与锁定</t>
+  </si>
+  <si>
+    <t>E5: 搬运任务管理</t>
+  </si>
+  <si>
+    <t>E4</t>
+  </si>
+  <si>
+    <t>US-E5-01: 搬运任务自动创建</t>
+  </si>
+  <si>
+    <t>US-E5-02: 搬运任务状态跟踪与异常处理</t>
+  </si>
+  <si>
+    <t>E5-01</t>
+  </si>
+  <si>
+    <t>E6: 双向校验机制</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>US-E6-01: 灵活顺序支持</t>
+  </si>
+  <si>
+    <t>US-E6-02: 清单导入时校验</t>
+  </si>
+  <si>
+    <t>E6-01</t>
+  </si>
+  <si>
+    <t>US-E6-03: 到货登记时校验</t>
+  </si>
+  <si>
+    <t>US-E6-04: 箱数不匹配处理</t>
+  </si>
+  <si>
+    <t>E6-02/03</t>
+  </si>
+  <si>
+    <t>US-E6-05: 校验审计日志</t>
+  </si>
+  <si>
+    <t>US-E6-06: 校验门禁控制</t>
+  </si>
+  <si>
+    <t>E1: QMS 集成与抽检策略</t>
+  </si>
+  <si>
+    <t>US-E1-01: QMS API 集成</t>
+  </si>
+  <si>
+    <t>US-E1-02: 抽检策略计算</t>
+  </si>
+  <si>
+    <t>E1-01</t>
+  </si>
+  <si>
+    <t>US-E1-03: 待送检列表生成</t>
+  </si>
+  <si>
+    <t>E1-02</t>
+  </si>
+  <si>
+    <t>US-E1-04: 拉动式工作流</t>
+  </si>
+  <si>
+    <t>E1-03</t>
+  </si>
+  <si>
+    <t>E2: IQC 检验管理</t>
+  </si>
+  <si>
+    <t>US-E2-01: IQC 呼叫机制</t>
+  </si>
+  <si>
+    <t>US-E2-02: 优先级调整</t>
+  </si>
+  <si>
+    <t>US-E2-03: 取样记录 PDA</t>
+  </si>
+  <si>
+    <t>US-E2-04: 归还记录 PDA</t>
+  </si>
+  <si>
+    <t>E2-03</t>
+  </si>
+  <si>
+    <t>US-E2-05: 检验完成确认</t>
+  </si>
+  <si>
+    <t>E2-04</t>
+  </si>
+  <si>
+    <t>E3: 路由与复判处理</t>
+  </si>
+  <si>
+    <t>E2</t>
+  </si>
+  <si>
+    <t>US-E3-01: 检验结果路由</t>
+  </si>
+  <si>
+    <t>E2-05</t>
+  </si>
+  <si>
+    <t>US-E3-02: 复判结果处理</t>
+  </si>
+  <si>
+    <t>US-E3-03: 复判完成 PDA</t>
+  </si>
+  <si>
+    <t>E3-02</t>
+  </si>
+  <si>
+    <t>E4: 栈板操作与不良品处理</t>
+  </si>
+  <si>
+    <t>US-E4-01: 栈板拆分 PDA</t>
+  </si>
+  <si>
+    <t>US-E4-02: 不良品处理</t>
+  </si>
+  <si>
+    <t>E5: Web 界面开发</t>
+  </si>
+  <si>
+    <t>E1, E2, E3</t>
+  </si>
+  <si>
+    <t>US-E5-01: 待送检列表页面</t>
+  </si>
+  <si>
+    <t>US-E5-02: 优先级调整对话框</t>
+  </si>
+  <si>
+    <t>E2-02</t>
+  </si>
+  <si>
+    <t>US-E5-03: 检验完成页面</t>
+  </si>
+  <si>
+    <t>US-E5-04: 复判处理页面</t>
+  </si>
+  <si>
+    <t>E6: PDA 界面开发</t>
+  </si>
+  <si>
+    <t>E2, E3, E4</t>
+  </si>
+  <si>
+    <t>US-E6-01: 取样记录界面</t>
+  </si>
+  <si>
+    <t>US-E6-02: 归还记录界面</t>
+  </si>
+  <si>
+    <t>US-E6-03: 拆板作业界面</t>
+  </si>
+  <si>
+    <t>US-E6-04: 复判完成界面</t>
+  </si>
+  <si>
+    <t>E1: 基础设施与核心架构</t>
+  </si>
+  <si>
+    <t>US-E1-01: 项目初始化与前后端环境搭建</t>
+  </si>
+  <si>
+    <t>US-E1-02: 数据库模型与迁移框架</t>
+  </si>
+  <si>
+    <t>US-E1-03: Redis 基础设施封装</t>
+  </si>
+  <si>
+    <t>US-E1-04: 统一日志与异常处理</t>
+  </si>
+  <si>
+    <t>E2: 设备管理与健康监控</t>
+  </si>
+  <si>
+    <t>US-E2-01: 设备主数据管理 API</t>
+  </si>
+  <si>
+    <t>US-E2-02: 设备健康监控服务 (后台任务)</t>
+  </si>
+  <si>
+    <t>US-E2-03: 设备状态缓存机制</t>
+  </si>
+  <si>
+    <t>E1-03, E2-02</t>
+  </si>
+  <si>
+    <t>E3: 任务调度引擎</t>
+  </si>
+  <si>
+    <t>E1, E2</t>
+  </si>
+  <si>
+    <t>US-E3-01: 任务状态机与领域模型</t>
+  </si>
+  <si>
+    <t>US-E3-02: 北向任务创建 API</t>
+  </si>
+  <si>
+    <t>US-E3-03: 基于 Redis 的优先级队列</t>
+  </si>
+  <si>
+    <t>E1-03, E3-01</t>
+  </si>
+  <si>
+    <t>US-E3-04: 任务调度器 Worker</t>
+  </si>
+  <si>
+    <t>E3-03, E2-03</t>
+  </si>
+  <si>
+    <t>US-E3-05: 并发控制机制</t>
+  </si>
+  <si>
+    <t>E4: 南向接口与可靠性</t>
+  </si>
+  <si>
+    <t>US-E4-01: ECS 客户端与协议适配</t>
+  </si>
+  <si>
+    <t>US-E4-02: 重试管理器 (指数退避)</t>
+  </si>
+  <si>
+    <t>US-E4-03: 回调接收 API</t>
+  </si>
+  <si>
+    <t>US-E4-04: 幂等性保障机制</t>
+  </si>
+  <si>
+    <t>E5: 北向接口与事件处理</t>
+  </si>
+  <si>
+    <t>US-E5-01: 设备事件分发器</t>
+  </si>
+  <si>
+    <t>US-E5-02: 任务取消流程</t>
+  </si>
+  <si>
+    <t>US-E1-01: 项目初始化与前后端环境搭建 (前端部分)</t>
+  </si>
+  <si>
+    <t>Backend E2</t>
+  </si>
+  <si>
+    <t>US-E2-04: 设备管理前端页面</t>
+  </si>
+  <si>
+    <t>Backend E2-01</t>
+  </si>
+  <si>
+    <t>E6: 管理监控界面</t>
+  </si>
+  <si>
+    <t>Backend E3, E5</t>
+  </si>
+  <si>
+    <t>US-E6-01: 任务监控看板</t>
+  </si>
+  <si>
+    <t>Backend E3-02</t>
+  </si>
+  <si>
+    <t>US-E6-02: 事件日志与审计</t>
+  </si>
+  <si>
+    <t>Backend E5-01</t>
+  </si>
+  <si>
+    <t>US-E6-03: 系统配置页面</t>
+  </si>
+  <si>
+    <t>Backend E1-04</t>
+  </si>
+  <si>
+    <t>E1: 装箱任务管理与调度</t>
+  </si>
+  <si>
+    <t>US-E1-01: 装箱任务呼叫界面</t>
+  </si>
+  <si>
+    <t>US-E1-02: 系统自动派送</t>
+  </si>
+  <si>
+    <t>US-E1-03: RCS调度集成</t>
+  </si>
+  <si>
+    <t>US-E1-04: PDA拆栈板界面</t>
+  </si>
+  <si>
+    <t>US-E1-05: 库存更新服务</t>
+  </si>
+  <si>
+    <t>US-E1-06: SignalR实时推送</t>
+  </si>
+  <si>
+    <t>E1-01, E1-04</t>
+  </si>
+  <si>
+    <t>E5: WMS-WES 集成</t>
+  </si>
+  <si>
+    <t>US-E5-01: 箱扫描完成通知</t>
+  </si>
+  <si>
+    <t>US-E5-02: 库存确认回调</t>
+  </si>
+  <si>
+    <t>US-E5-03: 货架状态同步</t>
+  </si>
+  <si>
+    <t>US-E5-04: 异常通知上报</t>
+  </si>
+  <si>
+    <t>E2: 货架管理与分箱算法</t>
+  </si>
+  <si>
+    <t>US-E2-01: 空架监控服务</t>
+  </si>
+  <si>
+    <t>US-E2-02: 货架状态管理</t>
+  </si>
+  <si>
+    <t>US-E2-03: 智能分箱算法核心</t>
+  </si>
+  <si>
+    <t>US-E2-04: 分箱结果计算</t>
+  </si>
+  <si>
+    <t>US-E2-05: 满架检测与切出</t>
+  </si>
+  <si>
+    <t>E2-02, E2-04</t>
+  </si>
+  <si>
+    <t>US-E2-06: WES北向API</t>
+  </si>
+  <si>
+    <t>E2-01, E2-02, E2-04</t>
+  </si>
+  <si>
+    <t>E3: 供应商协调与集成测试</t>
+  </si>
+  <si>
+    <t>US-E3-01: 供应商需求规格编写</t>
+  </si>
+  <si>
+    <t>US-E3-02: 接口契约定义与Mock服务</t>
+  </si>
+  <si>
+    <t>US-E3-03: 供应商对接支持与联调</t>
+  </si>
+  <si>
+    <t>US-E3-04: 集成测试场景设计与执行</t>
+  </si>
+  <si>
+    <t>US-E3-05: 性能验证与优化建议</t>
+  </si>
+  <si>
+    <t>E4: WES-供应商接口集成</t>
+  </si>
+  <si>
+    <t>US-E4-01: 视觉扫描结果接收</t>
+  </si>
+  <si>
+    <t>US-E4-02: 分箱指令下发</t>
+  </si>
+  <si>
+    <t>US-E4-03: 放入结果验证</t>
+  </si>
+  <si>
+    <t>US-E4-04: 设备状态同步</t>
+  </si>
+  <si>
+    <t>US-E4-05: 异常事件处理</t>
+  </si>
+  <si>
+    <t>E1: 混合入库决策引擎</t>
+  </si>
+  <si>
+    <t>E7</t>
+  </si>
+  <si>
+    <t>US-E1-01: 料箱容量分析算法</t>
+  </si>
+  <si>
+    <t>E7-01</t>
+  </si>
+  <si>
+    <t>US-E1-02: 空箱资源查询服务</t>
+  </si>
+  <si>
+    <t>E7-05</t>
+  </si>
+  <si>
+    <t>US-E1-03: 混合入库任务生成器</t>
+  </si>
+  <si>
+    <t>E1-01, E7-01</t>
+  </si>
+  <si>
+    <t>US-E1-04: 任务优先级排序引擎</t>
+  </si>
+  <si>
+    <t>US-E1-05: 决策配置管理</t>
+  </si>
+  <si>
+    <t>E2: 满箱交换协调器</t>
+  </si>
+  <si>
+    <t>E1, E7</t>
+  </si>
+  <si>
+    <t>US-E2-01: 五层货架调度服务</t>
+  </si>
+  <si>
+    <t>US-E2-02: 单层货架搬运协调</t>
+  </si>
+  <si>
+    <t>US-E2-03: CTU交换任务生成</t>
+  </si>
+  <si>
+    <t>US-E2-04: 交换结果处理器</t>
+  </si>
+  <si>
+    <t>US-E2-05: 库存转移确认服务</t>
+  </si>
+  <si>
+    <t>US-E2-06: 交换任务状态追踪</t>
+  </si>
+  <si>
+    <t>E3: 零散入库流水线协调器</t>
+  </si>
+  <si>
+    <t>US-E3-01: 单层货架工作区调度</t>
+  </si>
+  <si>
+    <t>US-E3-02: 料箱投入流水线协调</t>
+  </si>
+  <si>
+    <t>US-E3-03: 料箱条码识别处理</t>
+  </si>
+  <si>
+    <t>US-E3-04: 料盘PKG识别处理</t>
+  </si>
+  <si>
+    <t>US-E3-05: 投放指令生成器</t>
+  </si>
+  <si>
+    <t>US-E3-06: 投放结果处理器</t>
+  </si>
+  <si>
+    <t>E3-05</t>
+  </si>
+  <si>
+    <t>US-E3-07: 料箱完成与送回协调</t>
+  </si>
+  <si>
+    <t>E3-06</t>
+  </si>
+  <si>
+    <t>US-E3-08: 循环任务调度器</t>
+  </si>
+  <si>
+    <t>E3-07</t>
+  </si>
+  <si>
+    <t>E4: 空货架回收管理</t>
+  </si>
+  <si>
+    <t>E2, E3</t>
+  </si>
+  <si>
+    <t>US-E4-01: 空货架判断逻辑</t>
+  </si>
+  <si>
+    <t>US-E4-02: 空货架回收任务生成</t>
+  </si>
+  <si>
+    <t>US-E4-03: 货架状态更新服务</t>
+  </si>
+  <si>
+    <t>E5: WES 监控仪表板</t>
+  </si>
+  <si>
+    <t>E1-E4</t>
+  </si>
+  <si>
+    <t>US-E5-01: 实时任务监控界面</t>
+  </si>
+  <si>
+    <t>US-E5-02: 流水线状态监控</t>
+  </si>
+  <si>
+    <t>US-E5-03: 设备健康度监控</t>
+  </si>
+  <si>
+    <t>US-E5-04: 统计指标仪表板</t>
+  </si>
+  <si>
+    <t>US-E5-05: WebSocket 实时推送</t>
+  </si>
+  <si>
+    <t>E6: 异常处理与降级机制</t>
+  </si>
+  <si>
+    <t>US-E6-01: 异常检测与分类</t>
+  </si>
+  <si>
+    <t>US-E6-02: 异常任务处理界面</t>
+  </si>
+  <si>
+    <t>US-E6-03: 重试与降级策略</t>
+  </si>
+  <si>
+    <t>US-E6-04: 告警通知服务</t>
+  </si>
+  <si>
+    <t>US-E6-05: 审计日志记录</t>
+  </si>
+  <si>
+    <t>E7: 数据库模型与基础设施</t>
+  </si>
+  <si>
+    <t>US-E7-01: 核心数据表设计</t>
+  </si>
+  <si>
+    <t>US-E7-02: 数据库索引优化</t>
+  </si>
+  <si>
+    <t>US-E7-03: 数据库迁移脚本</t>
+  </si>
+  <si>
+    <t>US-E7-04: Redis 缓存设计</t>
+  </si>
+  <si>
+    <t>US-E7-05: API 接口框架</t>
+  </si>
+  <si>
+    <t>E8: WMS 操作员界面</t>
+  </si>
+  <si>
+    <t>E9</t>
+  </si>
+  <si>
+    <t>US-E8-01: 待入库缓存区叫料列表</t>
+  </si>
+  <si>
+    <t>US-E8-02: 手动叫料功能</t>
+  </si>
+  <si>
+    <t>E8-01</t>
+  </si>
+  <si>
+    <t>US-E8-03: 自动叫料模式切换</t>
+  </si>
+  <si>
+    <t>E8-02</t>
+  </si>
+  <si>
+    <t>US-E8-04: SignalR 实时状态更新</t>
+  </si>
+  <si>
+    <t>E9: WMS-WES 集成接口</t>
+  </si>
+  <si>
+    <t>US-E9-01: WMS 调用 WES 接口</t>
+  </si>
+  <si>
+    <t>US-E9-02: WES 调用 WMS 接口</t>
+  </si>
+  <si>
+    <t>US-E9-03: RCS 调度接口封装</t>
+  </si>
+  <si>
+    <t>US-E9-04: 接口错误处理</t>
+  </si>
+  <si>
+    <t>E9-01, E9-02</t>
+  </si>
+  <si>
+    <t>E10: 集成测试与验收</t>
+  </si>
+  <si>
+    <t>所有Epic</t>
+  </si>
+  <si>
+    <t>US-E10-01: 单元测试覆盖</t>
+  </si>
+  <si>
+    <t>E1-E9</t>
+  </si>
+  <si>
+    <t>US-E10-02: 集成测试场景</t>
+  </si>
+  <si>
+    <t>US-E10-03: 性能测试</t>
+  </si>
+  <si>
+    <t>E10-02</t>
+  </si>
+  <si>
+    <t>US-E10-04: 用户验收测试</t>
+  </si>
+  <si>
+    <t>WES 团队 13点 + WMS 团队 13点</t>
+  </si>
+  <si>
+    <t>WMS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>责任团队</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>任务项</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WES</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>协同</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMT 作业区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>WES 开发架构</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMT粗分区</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1: WMS 任务生成与货架规划</t>
+  </si>
+  <si>
+    <t>US-E1-01: 货架预规划算法实现</t>
+  </si>
+  <si>
+    <t>US-E1-02: 物料定位识别功能</t>
+  </si>
+  <si>
+    <t>US-E1-03: 批量货架调度功能</t>
+  </si>
+  <si>
+    <t>US-E1-04: WMS-WES 任务下发 API</t>
+  </si>
+  <si>
+    <t>E1-01, E1-02</t>
+  </si>
+  <si>
+    <t>US-E1-05: 料盘级物料追踪数据模型</t>
+  </si>
+  <si>
+    <t>E9: 异常处理与人工兜底</t>
+  </si>
+  <si>
+    <t>US-E9-01: 异常检测与告警</t>
+  </si>
+  <si>
+    <t>E1-04</t>
+  </si>
+  <si>
+    <t>US-E9-02: 人工介入触发</t>
+  </si>
+  <si>
+    <t>E9-01</t>
+  </si>
+  <si>
+    <t>US-E9-03: PDA 任务分配</t>
+  </si>
+  <si>
+    <t>E9-02</t>
+  </si>
+  <si>
+    <t>US-E9-04: 人工拣料工作流</t>
+  </si>
+  <si>
+    <t>E9-03</t>
+  </si>
+  <si>
+    <t>US-E9-05: 人工完成上报</t>
+  </si>
+  <si>
+    <t>E9-04</t>
+  </si>
+  <si>
+    <t>E2: WES 任务队列与编排</t>
+  </si>
+  <si>
+    <t>US-E2-01: 任务接收 API 端点</t>
+  </si>
+  <si>
+    <t>US-E2-02: 任务队列管理</t>
+  </si>
+  <si>
+    <t>US-E2-03: 设备状态监控</t>
+  </si>
+  <si>
+    <t>US-E2-04: 并发任务控制</t>
+  </si>
+  <si>
+    <t>US-E2-05: 任务调度算法</t>
+  </si>
+  <si>
+    <t>E3: CTU 批量上料操作</t>
+  </si>
+  <si>
+    <t>US-E3-01: 批量料箱取出协调</t>
+  </si>
+  <si>
+    <t>US-E3-02: 顺序料箱放入工作流</t>
+  </si>
+  <si>
+    <t>US-E3-03: PUT_FINISH 信号协调</t>
+  </si>
+  <si>
+    <t>US-E3-04: 出料口取料协调</t>
+  </si>
+  <si>
+    <t>US-E3-05: PICK_FINISH 信号协调</t>
+  </si>
+  <si>
+    <t>E4: 四识别点位集成</t>
+  </si>
+  <si>
+    <t>US-E4-01: 识别点 1 - 料箱码识别区</t>
+  </si>
+  <si>
+    <t>US-E4-02: 识别点 2 - 工作位料箱方向识别</t>
+  </si>
+  <si>
+    <t>US-E4-03: 识别点 3 - 料盘 PKG 码验证</t>
+  </si>
+  <si>
+    <t>US-E4-04: 识别点 4 - 出料口料箱扫码</t>
+  </si>
+  <si>
+    <t>US-E4-05: 料箱追踪状态机</t>
+  </si>
+  <si>
+    <t>E4-01, E4-02, E4-03, E4-04</t>
+  </si>
+  <si>
+    <t>E5: 退货架拣料操作</t>
+  </si>
+  <si>
+    <t>E2, E4</t>
+  </si>
+  <si>
+    <t>US-E5-01: 退货架到位确认</t>
+  </si>
+  <si>
+    <t>US-E5-02: 夹爪模式转移指令</t>
+  </si>
+  <si>
+    <t>E5-01, E4-02</t>
+  </si>
+  <si>
+    <t>US-E5-03: 竖直放置协调</t>
+  </si>
+  <si>
+    <t>E5-02</t>
+  </si>
+  <si>
+    <t>US-E5-04: 库存更新协调</t>
+  </si>
+  <si>
+    <t>E5-03</t>
+  </si>
+  <si>
+    <t>E6: 流水线拣料操作</t>
+  </si>
+  <si>
+    <t>US-E6-01: 批量上料协调</t>
+  </si>
+  <si>
+    <t>US-E6-02: 料箱识别与验证</t>
+  </si>
+  <si>
+    <t>E4-01, E6-01</t>
+  </si>
+  <si>
+    <t>US-E6-03: 拣料指令生成（含工作高度）</t>
+  </si>
+  <si>
+    <t>E4-03, E6-02</t>
+  </si>
+  <si>
+    <t>US-E6-04: 机械臂吸盘模式拣料</t>
+  </si>
+  <si>
+    <t>E6-03</t>
+  </si>
+  <si>
+    <t>US-E6-05: 实时库存扣减</t>
+  </si>
+  <si>
+    <t>E6-04</t>
+  </si>
+  <si>
+    <t>US-E6-06: 料箱轮转与下一箱处理</t>
+  </si>
+  <si>
+    <t>E6-05</t>
+  </si>
+  <si>
+    <t>E7: 退料流水线错误处理</t>
+  </si>
+  <si>
+    <t>US-E7-01: 错误检测逻辑</t>
+  </si>
+  <si>
+    <t>E4-05</t>
+  </si>
+  <si>
+    <t>US-E7-02: 返回指令下发</t>
+  </si>
+  <si>
+    <t>US-E7-03: 流水线路径切换</t>
+  </si>
+  <si>
+    <t>E7-02</t>
+  </si>
+  <si>
+    <t>US-E7-04: CTU 返回处理</t>
+  </si>
+  <si>
+    <t>E7-03</t>
+  </si>
+  <si>
+    <t>US-E7-05: 重试机制（最多 3 次）</t>
+  </si>
+  <si>
+    <t>E7-04</t>
+  </si>
+  <si>
+    <t>US-E7-06: 错误日志与追踪</t>
+  </si>
+  <si>
+    <t>E8: 结果上报与库存同步</t>
+  </si>
+  <si>
+    <t>E3, E5, E6</t>
+  </si>
+  <si>
+    <t>US-E8-01: 实时库存扣减 API</t>
+  </si>
+  <si>
+    <t>E5-04, E6-05</t>
+  </si>
+  <si>
+    <t>US-E8-02: 任务完成上报</t>
+  </si>
+  <si>
+    <t>US-E8-03: 物料完成追踪</t>
+  </si>
+  <si>
+    <t>US-E8-04: 料盘级完成追踪</t>
+  </si>
+  <si>
+    <t>E8-03</t>
+  </si>
+  <si>
+    <t>SMT 发料</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -506,7 +1616,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -521,6 +1631,13 @@
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="Helvetica Neue"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="18"/>
@@ -566,6 +1683,27 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="微软雅黑 Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑 Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF333333"/>
+      <name val="微软雅黑 Light"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -589,7 +1727,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -610,6 +1748,27 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -945,1260 +2104,1728 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{945DC6DF-BE66-CF42-AA2D-016BA392A074}">
-  <dimension ref="A1:F70"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="22" customHeight="1"/>
+  <dimension ref="A1:F96"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="20" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="42.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="44.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="43.33203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="32.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.6640625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="16384" width="10.83203125" style="2"/>
+    <col min="1" max="1" width="26.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="42.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="44.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.33203125" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="32.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.6640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="16384" width="10.83203125" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="22" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="26">
+      <c r="A1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B1" s="6"/>
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:6" s="5" customFormat="1" ht="23">
+      <c r="A2" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="23">
+      <c r="A3" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="23">
+      <c r="A4" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="23">
+      <c r="A5" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="23">
+      <c r="A6" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="23">
+      <c r="A7" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="23">
+      <c r="A8" s="6" t="s">
+        <v>163</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="23">
+      <c r="A9" s="6" t="s">
+        <v>165</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="23">
+      <c r="A10" s="6" t="s">
+        <v>185</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="23">
+      <c r="A11" s="6"/>
+      <c r="B11" s="6"/>
+      <c r="C11" s="6"/>
+      <c r="D11" s="6"/>
+      <c r="E11" s="6"/>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" ht="26">
+      <c r="A12" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="6"/>
+      <c r="C12" s="6"/>
+      <c r="D12" s="6"/>
+      <c r="E12" s="6"/>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" s="5" customFormat="1" ht="23">
+      <c r="A13" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="23">
+      <c r="A14" s="6" t="s">
+        <v>169</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>170</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="23">
+      <c r="A15" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="23">
+      <c r="A16" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="23">
+      <c r="A17" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="C17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="23">
+      <c r="A18" s="6" t="s">
+        <v>173</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="C18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F18" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="23">
+      <c r="A19" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>176</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="23">
+      <c r="A20" s="6" t="s">
+        <v>177</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="C20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="23">
+      <c r="A21" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="23">
+      <c r="A22" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" ht="23">
+      <c r="A23" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="C23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F23" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" ht="23">
+      <c r="A24" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" ht="23">
+      <c r="A25" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>183</v>
+      </c>
+      <c r="C25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="26">
+      <c r="A27" s="2" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="2" spans="1:6" s="4" customFormat="1" ht="22" customHeight="1">
-      <c r="A2" s="3" t="s">
+    <row r="28" spans="1:6" s="5" customFormat="1" ht="23">
+      <c r="A28" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B28" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C28" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="3" t="s">
+      <c r="D28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E28" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F28" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="22" customHeight="1">
-      <c r="A3" s="5" t="s">
+    <row r="29" spans="1:6" ht="23">
+      <c r="A29" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B29" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="22" customHeight="1">
-      <c r="A4" s="5" t="s">
+      <c r="C29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" ht="23">
+      <c r="A30" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" s="6" t="s">
+      <c r="B30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="22" customHeight="1">
-      <c r="A5" s="5" t="s">
+      <c r="D30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E30" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="23">
+      <c r="A31" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B31" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C31" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="6" t="s">
+      <c r="D31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" s="7" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="22" customHeight="1">
-      <c r="A6" s="5" t="s">
+    <row r="32" spans="1:6" ht="23">
+      <c r="A32" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="6" t="s">
+      <c r="B32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C32" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D32" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="22" customHeight="1">
-      <c r="A7" s="5" t="s">
+      <c r="E32" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" ht="23">
+      <c r="A33" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B33" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="22" customHeight="1">
-      <c r="A8" s="5" t="s">
+      <c r="C33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" ht="23">
+      <c r="A34" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="6" t="s">
+      <c r="B34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D34" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="22" customHeight="1">
-      <c r="A9" s="5" t="s">
+      <c r="E34" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" ht="23">
+      <c r="A35" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C9" s="6" t="s">
+      <c r="B35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C35" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="22" customHeight="1">
-      <c r="A10" s="5" t="s">
+      <c r="D35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E35" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" ht="23">
+      <c r="A36" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C10" s="6" t="s">
+      <c r="B36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C36" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="D10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="22" customHeight="1">
-      <c r="A11" s="5" t="s">
+      <c r="D36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" ht="23">
+      <c r="A37" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C11" s="6" t="s">
+      <c r="B37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C37" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="22" customHeight="1">
-      <c r="A12" s="5" t="s">
+      <c r="D37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F37" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" ht="23">
+      <c r="A38" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="6" t="s">
+      <c r="B38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D38" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="E12" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="22" customHeight="1">
-      <c r="A13" s="5" t="s">
+      <c r="E38" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F38" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" ht="23">
+      <c r="A39" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B39" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C39" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="22" customHeight="1">
-      <c r="A14" s="5" t="s">
+      <c r="D39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F39" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" ht="23">
+      <c r="A40" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6" t="s">
+      <c r="B40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="D14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="22" customHeight="1">
-      <c r="A15" s="5" t="s">
+      <c r="D40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" ht="23">
+      <c r="A41" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B41" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C41" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="D41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" s="7" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" spans="1:6" ht="22" customHeight="1">
-      <c r="A16" s="5" t="s">
+    <row r="42" spans="1:6" ht="23">
+      <c r="A42" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B42" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C42" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D42" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="22" customHeight="1">
-      <c r="A18" s="1" t="s">
+      <c r="E42" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" ht="26">
+      <c r="A44" s="2" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="19" spans="1:6" s="4" customFormat="1" ht="22" customHeight="1">
-      <c r="A19" s="3" t="s">
+    <row r="45" spans="1:6" s="5" customFormat="1" ht="23">
+      <c r="A45" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B45" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C45" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E19" s="3" t="s">
+      <c r="D45" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E45" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F19" s="3" t="s">
+      <c r="F45" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:6" ht="22" customHeight="1">
-      <c r="A20" s="5" t="s">
+    <row r="46" spans="1:6" ht="23">
+      <c r="A46" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C20" s="6" t="s">
+      <c r="B46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C46" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="22" customHeight="1">
-      <c r="A21" s="5" t="s">
+      <c r="D46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E46" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" ht="23">
+      <c r="A47" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C21" s="6" t="s">
+      <c r="B47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C47" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="22" customHeight="1">
-      <c r="A22" s="5" t="s">
+      <c r="D47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" ht="23">
+      <c r="A48" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="B22" s="6" t="s">
+      <c r="B48" s="7" t="s">
         <v>48</v>
       </c>
-      <c r="C22" s="6" t="s">
+      <c r="C48" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="D22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="22" customHeight="1">
-      <c r="A23" s="5" t="s">
+      <c r="D48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="23">
+      <c r="A49" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C23" s="6" t="s">
+      <c r="B49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C49" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" ht="22" customHeight="1">
-      <c r="A24" s="5" t="s">
+      <c r="D49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="23">
+      <c r="A50" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B24" s="6" t="s">
+      <c r="B50" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C24" s="6" t="s">
+      <c r="C50" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="D24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" s="6" t="s">
+      <c r="D50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" s="7" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:6" ht="22" customHeight="1">
-      <c r="A25" s="5" t="s">
+    <row r="51" spans="1:6" ht="23">
+      <c r="A51" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C25" s="6" t="s">
+      <c r="B51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C51" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="D25" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E25" s="6" t="s">
+      <c r="D51" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E51" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="F25" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" ht="22" customHeight="1">
-      <c r="A26" s="5" t="s">
+      <c r="F51" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="23">
+      <c r="A52" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="6" t="s">
+      <c r="B52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C52" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E26" s="6" t="s">
+      <c r="D52" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="22" customHeight="1">
-      <c r="A27" s="5" t="s">
+      <c r="F52" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="23">
+      <c r="A53" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="B53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="22" customHeight="1">
-      <c r="A28" s="5" t="s">
+      <c r="E53" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="23">
+      <c r="A54" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D28" s="6" t="s">
+      <c r="B54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="22" customHeight="1">
-      <c r="A29" s="5" t="s">
+      <c r="E54" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" ht="23">
+      <c r="A55" s="6" t="s">
         <v>66</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="6" t="s">
+      <c r="B55" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="D55" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" ht="22" customHeight="1">
-      <c r="A30" s="5" t="s">
+      <c r="E55" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="23">
+      <c r="A56" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C30" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D30" s="6" t="s">
+      <c r="B56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D56" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" ht="22" customHeight="1">
-      <c r="A31" s="5" t="s">
+      <c r="E56" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" ht="23">
+      <c r="A57" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="6" t="s">
+      <c r="B57" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="6" t="s">
+      <c r="C57" s="7" t="s">
         <v>73</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="D57" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E31" s="6" t="s">
+      <c r="E57" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="F31" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" ht="22" customHeight="1">
-      <c r="A32" s="5" t="s">
+      <c r="F57" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" ht="23">
+      <c r="A58" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B32" s="6" t="s">
+      <c r="B58" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E32" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F32" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" ht="22" customHeight="1">
-      <c r="A33" s="5" t="s">
+      <c r="C58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="23">
+      <c r="A59" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="6" t="s">
+      <c r="B59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C59" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="D33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E33" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" ht="22" customHeight="1">
-      <c r="A34" s="5" t="s">
+      <c r="D59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="23">
+      <c r="A60" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="6" t="s">
+      <c r="B60" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C34" s="6" t="s">
+      <c r="C60" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="D34" s="6" t="s">
+      <c r="D60" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E34" s="6" t="s">
+      <c r="E60" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" ht="22" customHeight="1">
-      <c r="A35" s="5" t="s">
+      <c r="F60" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" ht="23">
+      <c r="A61" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="B35" s="6" t="s">
+      <c r="B61" s="7" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="6" t="s">
+      <c r="C61" s="7" t="s">
         <v>83</v>
       </c>
-      <c r="D35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F35" s="6" t="s">
+      <c r="D61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F61" s="7" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:6" ht="22" customHeight="1">
-      <c r="A37" s="1" t="s">
+    <row r="63" spans="1:6" ht="26">
+      <c r="A63" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="38" spans="1:6" s="4" customFormat="1" ht="22" customHeight="1">
-      <c r="A38" s="3" t="s">
+    <row r="64" spans="1:6" s="5" customFormat="1" ht="23">
+      <c r="A64" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B64" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C64" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="E38" s="3" t="s">
+      <c r="D64" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="E64" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="F38" s="3" t="s">
+      <c r="F64" s="4" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:6" ht="22" customHeight="1">
-      <c r="A39" s="5" t="s">
+    <row r="65" spans="1:6" ht="23">
+      <c r="A65" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="B39" s="6" t="s">
+      <c r="B65" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="C39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E39" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" ht="22" customHeight="1">
-      <c r="A40" s="5" t="s">
+      <c r="C65" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" ht="23">
+      <c r="A66" s="6" t="s">
         <v>87</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B66" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="C40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E40" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" ht="22" customHeight="1">
-      <c r="A41" s="5" t="s">
+      <c r="C66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F66" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" ht="23">
+      <c r="A67" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="B41" s="6" t="s">
+      <c r="B67" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="C41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E41" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" ht="22" customHeight="1">
-      <c r="A42" s="5" t="s">
+      <c r="C67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E67" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" ht="23">
+      <c r="A68" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="B42" s="6" t="s">
+      <c r="B68" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="C42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" ht="22" customHeight="1">
-      <c r="A43" s="5" t="s">
+      <c r="C68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" ht="23">
+      <c r="A69" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="B43" s="6" t="s">
+      <c r="B69" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="C43" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E43" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F43" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" ht="22" customHeight="1">
-      <c r="A44" s="5" t="s">
+      <c r="C69" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D69" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" ht="23">
+      <c r="A70" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="B44" s="6" t="s">
+      <c r="B70" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E44" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F44" s="6" t="s">
+      <c r="C70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E70" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" s="7" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="45" spans="1:6" ht="22" customHeight="1">
-      <c r="A45" s="5" t="s">
+    <row r="71" spans="1:6" ht="23">
+      <c r="A71" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="B45" s="6" t="s">
+      <c r="B71" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="C45" s="6" t="s">
+      <c r="C71" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="D45" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E45" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F45" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" ht="22" customHeight="1">
-      <c r="A46" s="5" t="s">
+      <c r="D71" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E71" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" ht="23">
+      <c r="A72" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C46" s="6" t="s">
+      <c r="B72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C72" s="7" t="s">
         <v>99</v>
       </c>
-      <c r="D46" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E46" s="6" t="s">
+      <c r="D72" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="F46" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" ht="22" customHeight="1">
-      <c r="A47" s="5" t="s">
+      <c r="F72" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" ht="23">
+      <c r="A73" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="B47" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="6" t="s">
+      <c r="B73" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C73" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="D47" s="6" t="s">
+      <c r="D73" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="E47" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F47" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" ht="22" customHeight="1">
-      <c r="A48" s="5" t="s">
+      <c r="E73" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" ht="23">
+      <c r="A74" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="B48" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C48" s="6" t="s">
+      <c r="B74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D48" s="6" t="s">
+      <c r="D74" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="E48" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F48" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" ht="22" customHeight="1">
-      <c r="A49" s="5" t="s">
+      <c r="E74" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" ht="23">
+      <c r="A75" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="B49" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="6" t="s">
+      <c r="B75" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="D49" s="6" t="s">
+      <c r="D75" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="E49" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F49" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" ht="22" customHeight="1">
-      <c r="A50" s="5" t="s">
+      <c r="E75" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" ht="23">
+      <c r="A76" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="B50" s="6" t="s">
+      <c r="B76" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C50" s="6" t="s">
+      <c r="C76" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D50" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E50" s="6" t="s">
+      <c r="D76" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E76" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="F50" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" ht="22" customHeight="1">
-      <c r="A51" s="5" t="s">
+      <c r="F76" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" ht="23">
+      <c r="A77" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="B51" s="6" t="s">
+      <c r="B77" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="6" t="s">
+      <c r="C77" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="D51" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E51" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F51" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" ht="22" customHeight="1">
-      <c r="A52" s="5" t="s">
+      <c r="D77" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E77" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F77" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" ht="23">
+      <c r="A78" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="6" t="s">
+      <c r="B78" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="C52" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E52" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F52" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" ht="22" customHeight="1">
-      <c r="A53" s="5" t="s">
+      <c r="C78" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E78" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F78" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" ht="23">
+      <c r="A79" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B53" s="6" t="s">
+      <c r="B79" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C53" s="6" t="s">
+      <c r="C79" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="D79" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E53" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F53" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" ht="22" customHeight="1">
-      <c r="A54" s="5" t="s">
+      <c r="E79" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F79" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" ht="23">
+      <c r="A80" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="B54" s="6" t="s">
+      <c r="B80" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="C54" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="E54" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F54" s="6" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" ht="22" customHeight="1">
-      <c r="A56" s="5" t="s">
+      <c r="C80" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D80" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="E80" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F80" s="7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" ht="23">
+      <c r="A82" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B56" s="5"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="5"/>
-      <c r="E56" s="5"/>
-    </row>
-    <row r="57" spans="1:6" ht="22" customHeight="1">
-      <c r="A57" s="3" t="s">
+      <c r="B82" s="6"/>
+      <c r="C82" s="6"/>
+      <c r="D82" s="6"/>
+      <c r="E82" s="6"/>
+    </row>
+    <row r="83" spans="1:6" ht="23">
+      <c r="A83" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B83" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C83" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="D83" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="E83" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="F83" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:6" ht="22" customHeight="1">
-      <c r="A58" s="5" t="s">
+    <row r="84" spans="1:6" ht="23">
+      <c r="A84" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B84" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D58" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F58" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" ht="22" customHeight="1">
-      <c r="A59" s="5" t="s">
+      <c r="D84" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E84" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F84" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" ht="23">
+      <c r="A85" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B85" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D59" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" ht="22" customHeight="1">
-      <c r="A60" s="5" t="s">
+      <c r="D85" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E85" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F85" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" ht="23">
+      <c r="A86" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B86" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D60" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F60" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" ht="22" customHeight="1">
-      <c r="A61" s="5" t="s">
+      <c r="D86" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E86" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F86" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" ht="23">
+      <c r="A87" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B87" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D61" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F61" s="5" t="s">
+      <c r="D87" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E87" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F87" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="62" spans="1:6" ht="22" customHeight="1">
-      <c r="A62" s="5" t="s">
+    <row r="88" spans="1:6" ht="23">
+      <c r="A88" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B88" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D88" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" ht="22" customHeight="1">
-      <c r="A63" s="5" t="s">
+      <c r="E88" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F88" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" ht="23">
+      <c r="A89" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B89" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="D63" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E63" s="5" t="s">
+      <c r="D89" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E89" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F63" s="5" t="s">
+      <c r="F89" s="6" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="64" spans="1:6" ht="22" customHeight="1">
-      <c r="A64" s="5" t="s">
+    <row r="90" spans="1:6" ht="23">
+      <c r="A90" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B90" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="D64" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E64" s="5" t="s">
+      <c r="D90" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E90" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F64" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" ht="22" customHeight="1">
-      <c r="A65" s="5" t="s">
+      <c r="F90" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="23">
+      <c r="A91" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="B65" s="5" t="s">
+      <c r="B91" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="D65" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" s="5" t="s">
+      <c r="D91" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F91" s="6" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="1:6" ht="22" customHeight="1">
-      <c r="A66" s="5" t="s">
+    <row r="92" spans="1:6" ht="23">
+      <c r="A92" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B92" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D66" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F66" s="5" t="s">
+      <c r="D92" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F92" s="6" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="67" spans="1:6" ht="22" customHeight="1">
-      <c r="A67" s="5" t="s">
+    <row r="93" spans="1:6" ht="23">
+      <c r="A93" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B67" s="5" t="s">
+      <c r="B93" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="D67" s="5" t="s">
+      <c r="D93" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E67" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F67" s="5" t="s">
+      <c r="E93" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F93" s="6" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="68" spans="1:6" ht="22" customHeight="1">
-      <c r="A68" s="5" t="s">
+    <row r="94" spans="1:6" ht="23">
+      <c r="A94" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B94" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="D68" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" ht="22" customHeight="1">
-      <c r="A69" s="5" t="s">
+      <c r="D94" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" ht="23">
+      <c r="A95" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B69" s="5" t="s">
+      <c r="B95" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D69" s="5" t="s">
+      <c r="D95" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E69" s="5" t="s">
+      <c r="E95" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="F69" s="5" t="s">
+      <c r="F95" s="6" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="70" spans="1:6" ht="22" customHeight="1">
-      <c r="A70" s="5" t="s">
+    <row r="96" spans="1:6" ht="23">
+      <c r="A96" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="B70" s="5" t="s">
+      <c r="B96" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D70" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E70" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F70" s="5" t="s">
+      <c r="D96" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="6" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2207,4 +3834,4448 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850196EF-B3FB-4345-AB35-B6DAC38626B4}">
+  <dimension ref="A1:I236"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="26.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="31.1640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="69" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="39.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" ht="20">
+      <c r="A1" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="21">
+      <c r="A2" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C2" s="11">
+        <v>94</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>195</v>
+      </c>
+      <c r="E2" s="10"/>
+      <c r="F2" s="9">
+        <v>14</v>
+      </c>
+      <c r="G2" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H2" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="21">
+      <c r="A3" s="11"/>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="10"/>
+      <c r="E3" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="F3" s="10">
+        <v>2</v>
+      </c>
+      <c r="G3" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="21">
+      <c r="A4" s="11"/>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="F4" s="10">
+        <v>5</v>
+      </c>
+      <c r="G4" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H4" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="21">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="10"/>
+      <c r="E5" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="10">
+        <v>5</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H5" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="21">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="10" t="s">
+        <v>201</v>
+      </c>
+      <c r="F6" s="10">
+        <v>2</v>
+      </c>
+      <c r="G6" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="21">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="9" t="s">
+        <v>202</v>
+      </c>
+      <c r="E7" s="10"/>
+      <c r="F7" s="9">
+        <v>5</v>
+      </c>
+      <c r="G7" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H7" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="21">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="10"/>
+      <c r="E8" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="F8" s="10">
+        <v>3</v>
+      </c>
+      <c r="G8" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H8" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="21">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="10"/>
+      <c r="E9" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="F9" s="10">
+        <v>2</v>
+      </c>
+      <c r="G9" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="21">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="E10" s="10"/>
+      <c r="F10" s="9">
+        <v>21</v>
+      </c>
+      <c r="G10" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="21">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="10"/>
+      <c r="E11" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="F11" s="10">
+        <v>2</v>
+      </c>
+      <c r="G11" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H11" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="21">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="10"/>
+      <c r="E12" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="F12" s="10">
+        <v>3</v>
+      </c>
+      <c r="G12" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H12" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="21">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="10"/>
+      <c r="E13" s="10" t="s">
+        <v>211</v>
+      </c>
+      <c r="F13" s="10">
+        <v>5</v>
+      </c>
+      <c r="G13" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H13" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="21">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="10"/>
+      <c r="E14" s="10" t="s">
+        <v>212</v>
+      </c>
+      <c r="F14" s="10">
+        <v>3</v>
+      </c>
+      <c r="G14" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H14" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="21">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="10"/>
+      <c r="E15" s="10" t="s">
+        <v>214</v>
+      </c>
+      <c r="F15" s="10">
+        <v>5</v>
+      </c>
+      <c r="G15" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H15" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="21">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="10"/>
+      <c r="E16" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="F16" s="10">
+        <v>3</v>
+      </c>
+      <c r="G16" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H16" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="21">
+      <c r="A17" s="11"/>
+      <c r="B17" s="11"/>
+      <c r="C17" s="11"/>
+      <c r="D17" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" s="10"/>
+      <c r="F17" s="9">
+        <v>23</v>
+      </c>
+      <c r="G17" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H17" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="21">
+      <c r="A18" s="11"/>
+      <c r="B18" s="11"/>
+      <c r="C18" s="11"/>
+      <c r="D18" s="10"/>
+      <c r="E18" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F18" s="10">
+        <v>2</v>
+      </c>
+      <c r="G18" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H18" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="21">
+      <c r="A19" s="11"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11"/>
+      <c r="D19" s="10"/>
+      <c r="E19" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="F19" s="10">
+        <v>2</v>
+      </c>
+      <c r="G19" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H19" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="21">
+      <c r="A20" s="11"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="F20" s="10">
+        <v>8</v>
+      </c>
+      <c r="G20" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H20" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="21">
+      <c r="A21" s="11"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10" t="s">
+        <v>224</v>
+      </c>
+      <c r="F21" s="10">
+        <v>3</v>
+      </c>
+      <c r="G21" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H21" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="21">
+      <c r="A22" s="11"/>
+      <c r="B22" s="11"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="10"/>
+      <c r="E22" s="10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F22" s="10">
+        <v>5</v>
+      </c>
+      <c r="G22" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H22" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="21">
+      <c r="A23" s="11"/>
+      <c r="B23" s="11"/>
+      <c r="C23" s="11"/>
+      <c r="D23" s="10"/>
+      <c r="E23" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="F23" s="10">
+        <v>3</v>
+      </c>
+      <c r="G23" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H23" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="21">
+      <c r="A24" s="11"/>
+      <c r="B24" s="11"/>
+      <c r="C24" s="11"/>
+      <c r="D24" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="E24" s="10"/>
+      <c r="F24" s="9">
+        <v>10</v>
+      </c>
+      <c r="G24" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H24" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="21">
+      <c r="A25" s="11"/>
+      <c r="B25" s="11"/>
+      <c r="C25" s="11"/>
+      <c r="D25" s="10"/>
+      <c r="E25" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="F25" s="10">
+        <v>5</v>
+      </c>
+      <c r="G25" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H25" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="21">
+      <c r="A26" s="11"/>
+      <c r="B26" s="11"/>
+      <c r="C26" s="11"/>
+      <c r="D26" s="10"/>
+      <c r="E26" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="F26" s="10">
+        <v>5</v>
+      </c>
+      <c r="G26" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H26" s="10" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="21">
+      <c r="A27" s="11"/>
+      <c r="B27" s="11"/>
+      <c r="C27" s="11"/>
+      <c r="D27" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="E27" s="10"/>
+      <c r="F27" s="9">
+        <v>21</v>
+      </c>
+      <c r="G27" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H27" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="21">
+      <c r="A28" s="11"/>
+      <c r="B28" s="11"/>
+      <c r="C28" s="11"/>
+      <c r="D28" s="10"/>
+      <c r="E28" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="F28" s="10">
+        <v>3</v>
+      </c>
+      <c r="G28" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H28" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="21">
+      <c r="A29" s="11"/>
+      <c r="B29" s="11"/>
+      <c r="C29" s="11"/>
+      <c r="D29" s="10"/>
+      <c r="E29" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="F29" s="10">
+        <v>3</v>
+      </c>
+      <c r="G29" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H29" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="21">
+      <c r="A30" s="11"/>
+      <c r="B30" s="11"/>
+      <c r="C30" s="11"/>
+      <c r="D30" s="10"/>
+      <c r="E30" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="F30" s="10">
+        <v>5</v>
+      </c>
+      <c r="G30" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H30" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="21">
+      <c r="A31" s="11"/>
+      <c r="B31" s="11"/>
+      <c r="C31" s="11"/>
+      <c r="D31" s="10"/>
+      <c r="E31" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="F31" s="10">
+        <v>5</v>
+      </c>
+      <c r="G31" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H31" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="21">
+      <c r="A32" s="11"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="F32" s="10">
+        <v>2</v>
+      </c>
+      <c r="G32" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H32" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="21">
+      <c r="A33" s="11"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="F33" s="10">
+        <v>3</v>
+      </c>
+      <c r="G33" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H33" s="10" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="21">
+      <c r="A34" s="11" t="s">
+        <v>184</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C34" s="11">
+        <v>131</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="E34" s="10"/>
+      <c r="F34" s="9">
+        <v>21</v>
+      </c>
+      <c r="G34" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H34" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="21">
+      <c r="A35" s="11"/>
+      <c r="B35" s="11"/>
+      <c r="C35" s="11"/>
+      <c r="D35" s="10"/>
+      <c r="E35" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="F35" s="10">
+        <v>5</v>
+      </c>
+      <c r="G35" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H35" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="21">
+      <c r="A36" s="11"/>
+      <c r="B36" s="11"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="10"/>
+      <c r="E36" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F36" s="10">
+        <v>3</v>
+      </c>
+      <c r="G36" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H36" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="21">
+      <c r="A37" s="11"/>
+      <c r="B37" s="11"/>
+      <c r="C37" s="11"/>
+      <c r="D37" s="10"/>
+      <c r="E37" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="F37" s="10">
+        <v>5</v>
+      </c>
+      <c r="G37" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H37" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="21">
+      <c r="A38" s="11"/>
+      <c r="B38" s="11"/>
+      <c r="C38" s="11"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="F38" s="10">
+        <v>8</v>
+      </c>
+      <c r="G38" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H38" s="10" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="21">
+      <c r="A39" s="11"/>
+      <c r="B39" s="11"/>
+      <c r="C39" s="11"/>
+      <c r="D39" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="E39" s="10"/>
+      <c r="F39" s="9">
+        <v>34</v>
+      </c>
+      <c r="G39" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H39" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="21">
+      <c r="A40" s="11"/>
+      <c r="B40" s="11"/>
+      <c r="C40" s="11"/>
+      <c r="D40" s="10"/>
+      <c r="E40" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="F40" s="10">
+        <v>8</v>
+      </c>
+      <c r="G40" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H40" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="21">
+      <c r="A41" s="11"/>
+      <c r="B41" s="11"/>
+      <c r="C41" s="11"/>
+      <c r="D41" s="10"/>
+      <c r="E41" s="10" t="s">
+        <v>253</v>
+      </c>
+      <c r="F41" s="10">
+        <v>3</v>
+      </c>
+      <c r="G41" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H41" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="21">
+      <c r="A42" s="11"/>
+      <c r="B42" s="11"/>
+      <c r="C42" s="11"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="10">
+        <v>5</v>
+      </c>
+      <c r="G42" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H42" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="21">
+      <c r="A43" s="11"/>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="10"/>
+      <c r="E43" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="F43" s="10">
+        <v>5</v>
+      </c>
+      <c r="G43" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H43" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="21">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="F44" s="10">
+        <v>13</v>
+      </c>
+      <c r="G44" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H44" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="21">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="E45" s="10"/>
+      <c r="F45" s="9">
+        <v>21</v>
+      </c>
+      <c r="G45" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H45" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="21">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="10"/>
+      <c r="E46" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="F46" s="10">
+        <v>8</v>
+      </c>
+      <c r="G46" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H46" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="21">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="10"/>
+      <c r="E47" s="10" t="s">
+        <v>263</v>
+      </c>
+      <c r="F47" s="10">
+        <v>8</v>
+      </c>
+      <c r="G47" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="21">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="10"/>
+      <c r="E48" s="10" t="s">
+        <v>264</v>
+      </c>
+      <c r="F48" s="10">
+        <v>5</v>
+      </c>
+      <c r="G48" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H48" s="10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="21">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="E49" s="10"/>
+      <c r="F49" s="9">
+        <v>13</v>
+      </c>
+      <c r="G49" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H49" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="21">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="10"/>
+      <c r="E50" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="F50" s="10">
+        <v>8</v>
+      </c>
+      <c r="G50" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H50" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="21">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="F51" s="10">
+        <v>5</v>
+      </c>
+      <c r="G51" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H51" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="21">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="E52" s="10"/>
+      <c r="F52" s="9">
+        <v>21</v>
+      </c>
+      <c r="G52" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H52" s="10" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="21">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="10"/>
+      <c r="E53" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="F53" s="10">
+        <v>8</v>
+      </c>
+      <c r="G53" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H53" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="21">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="10"/>
+      <c r="E54" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="F54" s="10">
+        <v>3</v>
+      </c>
+      <c r="G54" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H54" s="10" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="21">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="F55" s="10">
+        <v>8</v>
+      </c>
+      <c r="G55" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H55" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="21">
+      <c r="A56" s="11"/>
+      <c r="B56" s="11"/>
+      <c r="C56" s="11"/>
+      <c r="D56" s="10"/>
+      <c r="E56" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="F56" s="10">
+        <v>2</v>
+      </c>
+      <c r="G56" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H56" s="10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="21">
+      <c r="A57" s="11"/>
+      <c r="B57" s="11"/>
+      <c r="C57" s="11"/>
+      <c r="D57" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="E57" s="10"/>
+      <c r="F57" s="9">
+        <v>21</v>
+      </c>
+      <c r="G57" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H57" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="21">
+      <c r="A58" s="11"/>
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="10"/>
+      <c r="E58" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="F58" s="10">
+        <v>5</v>
+      </c>
+      <c r="G58" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H58" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="21">
+      <c r="A59" s="11"/>
+      <c r="B59" s="11"/>
+      <c r="C59" s="11"/>
+      <c r="D59" s="10"/>
+      <c r="E59" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="F59" s="10">
+        <v>5</v>
+      </c>
+      <c r="G59" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H59" s="10" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="21">
+      <c r="A60" s="11"/>
+      <c r="B60" s="11"/>
+      <c r="C60" s="11"/>
+      <c r="D60" s="10"/>
+      <c r="E60" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F60" s="10">
+        <v>8</v>
+      </c>
+      <c r="G60" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H60" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="21">
+      <c r="A61" s="11"/>
+      <c r="B61" s="11"/>
+      <c r="C61" s="11"/>
+      <c r="D61" s="10"/>
+      <c r="E61" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="F61" s="10">
+        <v>3</v>
+      </c>
+      <c r="G61" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H61" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="21">
+      <c r="A62" s="11" t="s">
+        <v>438</v>
+      </c>
+      <c r="B62" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C62" s="11">
+        <v>71</v>
+      </c>
+      <c r="D62" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E62" s="10"/>
+      <c r="F62" s="9">
+        <v>13</v>
+      </c>
+      <c r="G62" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H62" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="21">
+      <c r="A63" s="11"/>
+      <c r="B63" s="11"/>
+      <c r="C63" s="11"/>
+      <c r="D63" s="10"/>
+      <c r="E63" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="F63" s="10">
+        <v>3</v>
+      </c>
+      <c r="G63" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H63" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="21">
+      <c r="A64" s="11"/>
+      <c r="B64" s="11"/>
+      <c r="C64" s="11"/>
+      <c r="D64" s="10"/>
+      <c r="E64" s="10" t="s">
+        <v>284</v>
+      </c>
+      <c r="F64" s="10">
+        <v>5</v>
+      </c>
+      <c r="G64" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H64" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="21">
+      <c r="A65" s="11"/>
+      <c r="B65" s="11"/>
+      <c r="C65" s="11"/>
+      <c r="D65" s="10"/>
+      <c r="E65" s="10" t="s">
+        <v>285</v>
+      </c>
+      <c r="F65" s="10">
+        <v>2</v>
+      </c>
+      <c r="G65" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H65" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="21">
+      <c r="A66" s="11"/>
+      <c r="B66" s="11"/>
+      <c r="C66" s="11"/>
+      <c r="D66" s="10"/>
+      <c r="E66" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="F66" s="10">
+        <v>3</v>
+      </c>
+      <c r="G66" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H66" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="21">
+      <c r="A67" s="11"/>
+      <c r="B67" s="11"/>
+      <c r="C67" s="11"/>
+      <c r="D67" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="E67" s="10"/>
+      <c r="F67" s="9">
+        <v>13</v>
+      </c>
+      <c r="G67" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H67" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="21">
+      <c r="A68" s="11"/>
+      <c r="B68" s="11"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="10"/>
+      <c r="E68" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="F68" s="10">
+        <v>3</v>
+      </c>
+      <c r="G68" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H68" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="21">
+      <c r="A69" s="11"/>
+      <c r="B69" s="11"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="10"/>
+      <c r="E69" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="F69" s="10">
+        <v>8</v>
+      </c>
+      <c r="G69" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H69" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="21">
+      <c r="A70" s="11"/>
+      <c r="B70" s="11"/>
+      <c r="C70" s="11"/>
+      <c r="D70" s="10"/>
+      <c r="E70" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="F70" s="10">
+        <v>2</v>
+      </c>
+      <c r="G70" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H70" s="10" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="21">
+      <c r="A71" s="11"/>
+      <c r="B71" s="11"/>
+      <c r="C71" s="11"/>
+      <c r="D71" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="E71" s="10"/>
+      <c r="F71" s="9">
+        <v>24</v>
+      </c>
+      <c r="G71" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H71" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="21">
+      <c r="A72" s="11"/>
+      <c r="B72" s="11"/>
+      <c r="C72" s="11"/>
+      <c r="D72" s="10"/>
+      <c r="E72" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="F72" s="10">
+        <v>5</v>
+      </c>
+      <c r="G72" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H72" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="21">
+      <c r="A73" s="11"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10" t="s">
+        <v>295</v>
+      </c>
+      <c r="F73" s="10">
+        <v>3</v>
+      </c>
+      <c r="G73" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H73" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="21">
+      <c r="A74" s="11"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="F74" s="10">
+        <v>5</v>
+      </c>
+      <c r="G74" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H74" s="10" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="21">
+      <c r="A75" s="11"/>
+      <c r="B75" s="11"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="10"/>
+      <c r="E75" s="10" t="s">
+        <v>298</v>
+      </c>
+      <c r="F75" s="10">
+        <v>8</v>
+      </c>
+      <c r="G75" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H75" s="10" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="21">
+      <c r="A76" s="11"/>
+      <c r="B76" s="11"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="10"/>
+      <c r="E76" s="10" t="s">
+        <v>300</v>
+      </c>
+      <c r="F76" s="10">
+        <v>3</v>
+      </c>
+      <c r="G76" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H76" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="21">
+      <c r="A77" s="11"/>
+      <c r="B77" s="11"/>
+      <c r="C77" s="11"/>
+      <c r="D77" s="9" t="s">
+        <v>301</v>
+      </c>
+      <c r="E77" s="10"/>
+      <c r="F77" s="9">
+        <v>16</v>
+      </c>
+      <c r="G77" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H77" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="21">
+      <c r="A78" s="11"/>
+      <c r="B78" s="11"/>
+      <c r="C78" s="11"/>
+      <c r="D78" s="10"/>
+      <c r="E78" s="10" t="s">
+        <v>302</v>
+      </c>
+      <c r="F78" s="10">
+        <v>5</v>
+      </c>
+      <c r="G78" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H78" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="21">
+      <c r="A79" s="11"/>
+      <c r="B79" s="11"/>
+      <c r="C79" s="11"/>
+      <c r="D79" s="10"/>
+      <c r="E79" s="10" t="s">
+        <v>303</v>
+      </c>
+      <c r="F79" s="10">
+        <v>5</v>
+      </c>
+      <c r="G79" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H79" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="21">
+      <c r="A80" s="11"/>
+      <c r="B80" s="11"/>
+      <c r="C80" s="11"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10" t="s">
+        <v>304</v>
+      </c>
+      <c r="F80" s="10">
+        <v>3</v>
+      </c>
+      <c r="G80" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H80" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="21">
+      <c r="A81" s="11"/>
+      <c r="B81" s="11"/>
+      <c r="C81" s="11"/>
+      <c r="D81" s="10"/>
+      <c r="E81" s="10" t="s">
+        <v>305</v>
+      </c>
+      <c r="F81" s="10">
+        <v>3</v>
+      </c>
+      <c r="G81" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H81" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="21">
+      <c r="A82" s="11"/>
+      <c r="B82" s="11"/>
+      <c r="C82" s="11"/>
+      <c r="D82" s="9" t="s">
+        <v>306</v>
+      </c>
+      <c r="E82" s="10"/>
+      <c r="F82" s="9">
+        <v>5</v>
+      </c>
+      <c r="G82" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H82" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="21">
+      <c r="A83" s="11"/>
+      <c r="B83" s="11"/>
+      <c r="C83" s="11"/>
+      <c r="D83" s="10"/>
+      <c r="E83" s="10" t="s">
+        <v>307</v>
+      </c>
+      <c r="F83" s="10">
+        <v>5</v>
+      </c>
+      <c r="G83" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H83" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="21">
+      <c r="A84" s="11"/>
+      <c r="B84" s="11"/>
+      <c r="C84" s="11"/>
+      <c r="D84" s="10"/>
+      <c r="E84" s="10" t="s">
+        <v>308</v>
+      </c>
+      <c r="F84" s="10">
+        <v>3</v>
+      </c>
+      <c r="G84" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H84" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="21">
+      <c r="A85" s="11"/>
+      <c r="B85" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C85" s="11">
+        <v>21</v>
+      </c>
+      <c r="D85" s="9" t="s">
+        <v>282</v>
+      </c>
+      <c r="E85" s="10"/>
+      <c r="F85" s="9">
+        <v>3</v>
+      </c>
+      <c r="G85" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H85" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="21">
+      <c r="A86" s="11"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10" t="s">
+        <v>309</v>
+      </c>
+      <c r="F86" s="10">
+        <v>3</v>
+      </c>
+      <c r="G86" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H86" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="21">
+      <c r="A87" s="11"/>
+      <c r="B87" s="11"/>
+      <c r="C87" s="11"/>
+      <c r="D87" s="9" t="s">
+        <v>287</v>
+      </c>
+      <c r="E87" s="10"/>
+      <c r="F87" s="9">
+        <v>5</v>
+      </c>
+      <c r="G87" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H87" s="10" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="21">
+      <c r="A88" s="11"/>
+      <c r="B88" s="11"/>
+      <c r="C88" s="11"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10" t="s">
+        <v>311</v>
+      </c>
+      <c r="F88" s="10">
+        <v>5</v>
+      </c>
+      <c r="G88" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H88" s="10" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="21">
+      <c r="A89" s="11"/>
+      <c r="B89" s="11"/>
+      <c r="C89" s="11"/>
+      <c r="D89" s="9" t="s">
+        <v>313</v>
+      </c>
+      <c r="E89" s="10"/>
+      <c r="F89" s="9">
+        <v>11</v>
+      </c>
+      <c r="G89" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H89" s="10" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="21">
+      <c r="A90" s="11"/>
+      <c r="B90" s="11"/>
+      <c r="C90" s="11"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10" t="s">
+        <v>315</v>
+      </c>
+      <c r="F90" s="10">
+        <v>5</v>
+      </c>
+      <c r="G90" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H90" s="10" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="21">
+      <c r="A91" s="11"/>
+      <c r="B91" s="11"/>
+      <c r="C91" s="11"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10" t="s">
+        <v>317</v>
+      </c>
+      <c r="F91" s="10">
+        <v>3</v>
+      </c>
+      <c r="G91" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H91" s="10" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="21">
+      <c r="A92" s="11"/>
+      <c r="B92" s="11"/>
+      <c r="C92" s="11"/>
+      <c r="D92" s="10"/>
+      <c r="E92" s="10" t="s">
+        <v>319</v>
+      </c>
+      <c r="F92" s="10">
+        <v>3</v>
+      </c>
+      <c r="G92" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H92" s="10" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="21">
+      <c r="A93" s="11" t="s">
+        <v>439</v>
+      </c>
+      <c r="B93" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C93" s="11">
+        <v>32</v>
+      </c>
+      <c r="D93" s="9" t="s">
+        <v>321</v>
+      </c>
+      <c r="E93" s="10"/>
+      <c r="F93" s="9">
+        <v>22</v>
+      </c>
+      <c r="G93" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H93" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="21">
+      <c r="A94" s="11"/>
+      <c r="B94" s="11"/>
+      <c r="C94" s="11"/>
+      <c r="D94" s="10"/>
+      <c r="E94" s="10" t="s">
+        <v>322</v>
+      </c>
+      <c r="F94" s="10">
+        <v>5</v>
+      </c>
+      <c r="G94" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H94" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="21">
+      <c r="A95" s="11"/>
+      <c r="B95" s="11"/>
+      <c r="C95" s="11"/>
+      <c r="D95" s="10"/>
+      <c r="E95" s="10" t="s">
+        <v>323</v>
+      </c>
+      <c r="F95" s="10">
+        <v>3</v>
+      </c>
+      <c r="G95" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H95" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="21">
+      <c r="A96" s="11"/>
+      <c r="B96" s="11"/>
+      <c r="C96" s="11"/>
+      <c r="D96" s="10"/>
+      <c r="E96" s="10" t="s">
+        <v>324</v>
+      </c>
+      <c r="F96" s="10">
+        <v>5</v>
+      </c>
+      <c r="G96" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H96" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9" ht="21">
+      <c r="A97" s="11"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10" t="s">
+        <v>325</v>
+      </c>
+      <c r="F97" s="10">
+        <v>3</v>
+      </c>
+      <c r="G97" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H97" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9" ht="21">
+      <c r="A98" s="11"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10" t="s">
+        <v>326</v>
+      </c>
+      <c r="F98" s="10">
+        <v>3</v>
+      </c>
+      <c r="G98" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H98" s="10" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9" ht="21">
+      <c r="A99" s="11"/>
+      <c r="B99" s="11"/>
+      <c r="C99" s="11"/>
+      <c r="D99" s="10"/>
+      <c r="E99" s="10" t="s">
+        <v>327</v>
+      </c>
+      <c r="F99" s="10">
+        <v>3</v>
+      </c>
+      <c r="G99" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H99" s="10" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9" ht="21">
+      <c r="A100" s="11"/>
+      <c r="B100" s="11"/>
+      <c r="C100" s="11"/>
+      <c r="D100" s="9" t="s">
+        <v>329</v>
+      </c>
+      <c r="E100" s="10"/>
+      <c r="F100" s="9">
+        <v>10</v>
+      </c>
+      <c r="G100" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H100" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9" ht="21">
+      <c r="A101" s="11"/>
+      <c r="B101" s="11"/>
+      <c r="C101" s="11"/>
+      <c r="D101" s="10"/>
+      <c r="E101" s="10" t="s">
+        <v>330</v>
+      </c>
+      <c r="F101" s="10">
+        <v>2</v>
+      </c>
+      <c r="G101" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H101" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9" ht="21">
+      <c r="A102" s="11"/>
+      <c r="B102" s="11"/>
+      <c r="C102" s="11"/>
+      <c r="D102" s="10"/>
+      <c r="E102" s="10" t="s">
+        <v>331</v>
+      </c>
+      <c r="F102" s="10">
+        <v>3</v>
+      </c>
+      <c r="G102" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H102" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9" ht="21">
+      <c r="A103" s="11"/>
+      <c r="B103" s="11"/>
+      <c r="C103" s="11"/>
+      <c r="D103" s="10"/>
+      <c r="E103" s="10" t="s">
+        <v>332</v>
+      </c>
+      <c r="F103" s="10">
+        <v>3</v>
+      </c>
+      <c r="G103" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H103" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9" ht="21">
+      <c r="A104" s="11"/>
+      <c r="B104" s="11"/>
+      <c r="C104" s="11"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="F104" s="10">
+        <v>2</v>
+      </c>
+      <c r="G104" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H104" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9" ht="21">
+      <c r="A105" s="11"/>
+      <c r="B105" s="12" t="s">
+        <v>435</v>
+      </c>
+      <c r="C105" s="12">
+        <v>64</v>
+      </c>
+      <c r="D105" s="9" t="s">
+        <v>334</v>
+      </c>
+      <c r="E105" s="10"/>
+      <c r="F105" s="9">
+        <v>26</v>
+      </c>
+      <c r="G105" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H105" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I105" s="8"/>
+    </row>
+    <row r="106" spans="1:9" ht="21">
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="12"/>
+      <c r="D106" s="10"/>
+      <c r="E106" s="10" t="s">
+        <v>335</v>
+      </c>
+      <c r="F106" s="10">
+        <v>2</v>
+      </c>
+      <c r="G106" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H106" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I106" s="8"/>
+    </row>
+    <row r="107" spans="1:9" ht="21">
+      <c r="A107" s="11"/>
+      <c r="B107" s="12"/>
+      <c r="C107" s="12"/>
+      <c r="D107" s="10"/>
+      <c r="E107" s="10" t="s">
+        <v>336</v>
+      </c>
+      <c r="F107" s="10">
+        <v>5</v>
+      </c>
+      <c r="G107" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H107" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I107" s="8"/>
+    </row>
+    <row r="108" spans="1:9" ht="21">
+      <c r="A108" s="11"/>
+      <c r="B108" s="12"/>
+      <c r="C108" s="12"/>
+      <c r="D108" s="10"/>
+      <c r="E108" s="10" t="s">
+        <v>337</v>
+      </c>
+      <c r="F108" s="10">
+        <v>8</v>
+      </c>
+      <c r="G108" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H108" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I108" s="8"/>
+    </row>
+    <row r="109" spans="1:9" ht="21">
+      <c r="A109" s="11"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="12"/>
+      <c r="D109" s="10"/>
+      <c r="E109" s="10" t="s">
+        <v>338</v>
+      </c>
+      <c r="F109" s="10">
+        <v>5</v>
+      </c>
+      <c r="G109" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H109" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="I109" s="8"/>
+    </row>
+    <row r="110" spans="1:9" ht="21">
+      <c r="A110" s="11"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="12"/>
+      <c r="D110" s="10"/>
+      <c r="E110" s="10" t="s">
+        <v>339</v>
+      </c>
+      <c r="F110" s="10">
+        <v>3</v>
+      </c>
+      <c r="G110" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H110" s="10" t="s">
+        <v>340</v>
+      </c>
+      <c r="I110" s="8"/>
+    </row>
+    <row r="111" spans="1:9" ht="21">
+      <c r="A111" s="11"/>
+      <c r="B111" s="12"/>
+      <c r="C111" s="12"/>
+      <c r="D111" s="10"/>
+      <c r="E111" s="10" t="s">
+        <v>341</v>
+      </c>
+      <c r="F111" s="10">
+        <v>3</v>
+      </c>
+      <c r="G111" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H111" s="10" t="s">
+        <v>342</v>
+      </c>
+      <c r="I111" s="8"/>
+    </row>
+    <row r="112" spans="1:9" ht="21">
+      <c r="A112" s="11"/>
+      <c r="B112" s="12"/>
+      <c r="C112" s="12"/>
+      <c r="D112" s="9" t="s">
+        <v>343</v>
+      </c>
+      <c r="E112" s="10"/>
+      <c r="F112" s="9">
+        <v>21</v>
+      </c>
+      <c r="G112" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H112" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="I112" s="8"/>
+    </row>
+    <row r="113" spans="1:9" ht="21">
+      <c r="A113" s="11"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="12"/>
+      <c r="D113" s="10"/>
+      <c r="E113" s="10" t="s">
+        <v>344</v>
+      </c>
+      <c r="F113" s="10">
+        <v>3</v>
+      </c>
+      <c r="G113" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H113" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I113" s="8"/>
+    </row>
+    <row r="114" spans="1:9" ht="21">
+      <c r="A114" s="11"/>
+      <c r="B114" s="12"/>
+      <c r="C114" s="12"/>
+      <c r="D114" s="10"/>
+      <c r="E114" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="F114" s="10">
+        <v>5</v>
+      </c>
+      <c r="G114" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H114" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="I114" s="8"/>
+    </row>
+    <row r="115" spans="1:9" ht="21">
+      <c r="A115" s="11"/>
+      <c r="B115" s="12"/>
+      <c r="C115" s="12"/>
+      <c r="D115" s="10"/>
+      <c r="E115" s="10" t="s">
+        <v>346</v>
+      </c>
+      <c r="F115" s="10">
+        <v>5</v>
+      </c>
+      <c r="G115" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H115" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="I115" s="8"/>
+    </row>
+    <row r="116" spans="1:9" ht="21">
+      <c r="A116" s="11"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="12"/>
+      <c r="D116" s="10"/>
+      <c r="E116" s="10" t="s">
+        <v>347</v>
+      </c>
+      <c r="F116" s="10">
+        <v>5</v>
+      </c>
+      <c r="G116" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H116" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="I116" s="8"/>
+    </row>
+    <row r="117" spans="1:9" ht="21">
+      <c r="A117" s="11"/>
+      <c r="B117" s="12"/>
+      <c r="C117" s="12"/>
+      <c r="D117" s="10"/>
+      <c r="E117" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="F117" s="10">
+        <v>3</v>
+      </c>
+      <c r="G117" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H117" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="I117" s="8"/>
+    </row>
+    <row r="118" spans="1:9" ht="21">
+      <c r="A118" s="11"/>
+      <c r="B118" s="12"/>
+      <c r="C118" s="12"/>
+      <c r="D118" s="9" t="s">
+        <v>349</v>
+      </c>
+      <c r="E118" s="10"/>
+      <c r="F118" s="9">
+        <v>17</v>
+      </c>
+      <c r="G118" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H118" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I118" s="8"/>
+    </row>
+    <row r="119" spans="1:9" ht="21">
+      <c r="A119" s="11"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="12"/>
+      <c r="D119" s="10"/>
+      <c r="E119" s="10" t="s">
+        <v>350</v>
+      </c>
+      <c r="F119" s="10">
+        <v>3</v>
+      </c>
+      <c r="G119" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H119" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="I119" s="8"/>
+    </row>
+    <row r="120" spans="1:9" ht="21">
+      <c r="A120" s="11"/>
+      <c r="B120" s="12"/>
+      <c r="C120" s="12"/>
+      <c r="D120" s="10"/>
+      <c r="E120" s="10" t="s">
+        <v>351</v>
+      </c>
+      <c r="F120" s="10">
+        <v>3</v>
+      </c>
+      <c r="G120" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H120" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="I120" s="8"/>
+    </row>
+    <row r="121" spans="1:9" ht="21">
+      <c r="A121" s="11"/>
+      <c r="B121" s="12"/>
+      <c r="C121" s="12"/>
+      <c r="D121" s="10"/>
+      <c r="E121" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="F121" s="10">
+        <v>5</v>
+      </c>
+      <c r="G121" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H121" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="I121" s="8"/>
+    </row>
+    <row r="122" spans="1:9" ht="21">
+      <c r="A122" s="11"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="12"/>
+      <c r="D122" s="10"/>
+      <c r="E122" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F122" s="10">
+        <v>3</v>
+      </c>
+      <c r="G122" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H122" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I122" s="8"/>
+    </row>
+    <row r="123" spans="1:9" ht="21">
+      <c r="A123" s="11"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="12"/>
+      <c r="D123" s="10"/>
+      <c r="E123" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="F123" s="10">
+        <v>3</v>
+      </c>
+      <c r="G123" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H123" s="10" t="s">
+        <v>225</v>
+      </c>
+      <c r="I123" s="8"/>
+    </row>
+    <row r="124" spans="1:9" ht="21">
+      <c r="A124" s="11" t="s">
+        <v>437</v>
+      </c>
+      <c r="B124" s="11" t="s">
+        <v>435</v>
+      </c>
+      <c r="C124" s="11">
+        <v>143</v>
+      </c>
+      <c r="D124" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="E124" s="10"/>
+      <c r="F124" s="9">
+        <v>15</v>
+      </c>
+      <c r="G124" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H124" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I124" s="8"/>
+    </row>
+    <row r="125" spans="1:9" ht="21">
+      <c r="A125" s="11"/>
+      <c r="B125" s="11"/>
+      <c r="C125" s="11"/>
+      <c r="D125" s="10"/>
+      <c r="E125" s="10" t="s">
+        <v>357</v>
+      </c>
+      <c r="F125" s="10">
+        <v>3</v>
+      </c>
+      <c r="G125" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H125" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I125" s="8"/>
+    </row>
+    <row r="126" spans="1:9" ht="21">
+      <c r="A126" s="11"/>
+      <c r="B126" s="11"/>
+      <c r="C126" s="11"/>
+      <c r="D126" s="10"/>
+      <c r="E126" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="F126" s="10">
+        <v>2</v>
+      </c>
+      <c r="G126" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H126" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="I126" s="8"/>
+    </row>
+    <row r="127" spans="1:9" ht="21">
+      <c r="A127" s="11"/>
+      <c r="B127" s="11"/>
+      <c r="C127" s="11"/>
+      <c r="D127" s="10"/>
+      <c r="E127" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="F127" s="10">
+        <v>5</v>
+      </c>
+      <c r="G127" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H127" s="10" t="s">
+        <v>362</v>
+      </c>
+      <c r="I127" s="8"/>
+    </row>
+    <row r="128" spans="1:9" ht="21">
+      <c r="A128" s="11"/>
+      <c r="B128" s="11"/>
+      <c r="C128" s="11"/>
+      <c r="D128" s="10"/>
+      <c r="E128" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="F128" s="10">
+        <v>3</v>
+      </c>
+      <c r="G128" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H128" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="I128" s="8"/>
+    </row>
+    <row r="129" spans="1:9" ht="21">
+      <c r="A129" s="11"/>
+      <c r="B129" s="11"/>
+      <c r="C129" s="11"/>
+      <c r="D129" s="10"/>
+      <c r="E129" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="F129" s="10">
+        <v>2</v>
+      </c>
+      <c r="G129" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H129" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I129" s="8"/>
+    </row>
+    <row r="130" spans="1:9" ht="21">
+      <c r="A130" s="11"/>
+      <c r="B130" s="11"/>
+      <c r="C130" s="11"/>
+      <c r="D130" s="9" t="s">
+        <v>365</v>
+      </c>
+      <c r="E130" s="10"/>
+      <c r="F130" s="9">
+        <v>21</v>
+      </c>
+      <c r="G130" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H130" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="I130" s="8"/>
+    </row>
+    <row r="131" spans="1:9" ht="21">
+      <c r="A131" s="11"/>
+      <c r="B131" s="11"/>
+      <c r="C131" s="11"/>
+      <c r="D131" s="10"/>
+      <c r="E131" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="F131" s="10">
+        <v>5</v>
+      </c>
+      <c r="G131" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H131" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="I131" s="8"/>
+    </row>
+    <row r="132" spans="1:9" ht="21">
+      <c r="A132" s="11"/>
+      <c r="B132" s="11"/>
+      <c r="C132" s="11"/>
+      <c r="D132" s="10"/>
+      <c r="E132" s="10" t="s">
+        <v>368</v>
+      </c>
+      <c r="F132" s="10">
+        <v>3</v>
+      </c>
+      <c r="G132" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H132" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="I132" s="8"/>
+    </row>
+    <row r="133" spans="1:9" ht="21">
+      <c r="A133" s="11"/>
+      <c r="B133" s="11"/>
+      <c r="C133" s="11"/>
+      <c r="D133" s="10"/>
+      <c r="E133" s="10" t="s">
+        <v>369</v>
+      </c>
+      <c r="F133" s="10">
+        <v>5</v>
+      </c>
+      <c r="G133" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H133" s="10" t="s">
+        <v>273</v>
+      </c>
+      <c r="I133" s="8"/>
+    </row>
+    <row r="134" spans="1:9" ht="21">
+      <c r="A134" s="11"/>
+      <c r="B134" s="11"/>
+      <c r="C134" s="11"/>
+      <c r="D134" s="10"/>
+      <c r="E134" s="10" t="s">
+        <v>370</v>
+      </c>
+      <c r="F134" s="10">
+        <v>3</v>
+      </c>
+      <c r="G134" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H134" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="I134" s="8"/>
+    </row>
+    <row r="135" spans="1:9" ht="21">
+      <c r="A135" s="11"/>
+      <c r="B135" s="11"/>
+      <c r="C135" s="11"/>
+      <c r="D135" s="10"/>
+      <c r="E135" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="F135" s="10">
+        <v>3</v>
+      </c>
+      <c r="G135" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H135" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="I135" s="8"/>
+    </row>
+    <row r="136" spans="1:9" ht="21">
+      <c r="A136" s="11"/>
+      <c r="B136" s="11"/>
+      <c r="C136" s="11"/>
+      <c r="D136" s="10"/>
+      <c r="E136" s="10" t="s">
+        <v>372</v>
+      </c>
+      <c r="F136" s="10">
+        <v>2</v>
+      </c>
+      <c r="G136" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H136" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="I136" s="8"/>
+    </row>
+    <row r="137" spans="1:9" ht="21">
+      <c r="A137" s="11"/>
+      <c r="B137" s="11"/>
+      <c r="C137" s="11"/>
+      <c r="D137" s="9" t="s">
+        <v>373</v>
+      </c>
+      <c r="E137" s="10"/>
+      <c r="F137" s="9">
+        <v>37</v>
+      </c>
+      <c r="G137" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H137" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="I137" s="8"/>
+    </row>
+    <row r="138" spans="1:9" ht="21">
+      <c r="A138" s="11"/>
+      <c r="B138" s="11"/>
+      <c r="C138" s="11"/>
+      <c r="D138" s="10"/>
+      <c r="E138" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="F138" s="10">
+        <v>3</v>
+      </c>
+      <c r="G138" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H138" s="10" t="s">
+        <v>203</v>
+      </c>
+      <c r="I138" s="8"/>
+    </row>
+    <row r="139" spans="1:9" ht="21">
+      <c r="A139" s="11"/>
+      <c r="B139" s="11"/>
+      <c r="C139" s="11"/>
+      <c r="D139" s="10"/>
+      <c r="E139" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="F139" s="10">
+        <v>5</v>
+      </c>
+      <c r="G139" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H139" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="I139" s="8"/>
+    </row>
+    <row r="140" spans="1:9" ht="21">
+      <c r="A140" s="11"/>
+      <c r="B140" s="11"/>
+      <c r="C140" s="11"/>
+      <c r="D140" s="10"/>
+      <c r="E140" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="F140" s="10">
+        <v>5</v>
+      </c>
+      <c r="G140" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H140" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="I140" s="8"/>
+    </row>
+    <row r="141" spans="1:9" ht="21">
+      <c r="A141" s="11"/>
+      <c r="B141" s="11"/>
+      <c r="C141" s="11"/>
+      <c r="D141" s="10"/>
+      <c r="E141" s="10" t="s">
+        <v>377</v>
+      </c>
+      <c r="F141" s="10">
+        <v>5</v>
+      </c>
+      <c r="G141" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H141" s="10" t="s">
+        <v>213</v>
+      </c>
+      <c r="I141" s="8"/>
+    </row>
+    <row r="142" spans="1:9" ht="21">
+      <c r="A142" s="11"/>
+      <c r="B142" s="11"/>
+      <c r="C142" s="11"/>
+      <c r="D142" s="10"/>
+      <c r="E142" s="10" t="s">
+        <v>378</v>
+      </c>
+      <c r="F142" s="10">
+        <v>8</v>
+      </c>
+      <c r="G142" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H142" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="I142" s="8"/>
+    </row>
+    <row r="143" spans="1:9" ht="21">
+      <c r="A143" s="11"/>
+      <c r="B143" s="11"/>
+      <c r="C143" s="11"/>
+      <c r="D143" s="10"/>
+      <c r="E143" s="10" t="s">
+        <v>379</v>
+      </c>
+      <c r="F143" s="10">
+        <v>3</v>
+      </c>
+      <c r="G143" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H143" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="I143" s="8"/>
+    </row>
+    <row r="144" spans="1:9" ht="21">
+      <c r="A144" s="11"/>
+      <c r="B144" s="11"/>
+      <c r="C144" s="11"/>
+      <c r="D144" s="10"/>
+      <c r="E144" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="F144" s="10">
+        <v>5</v>
+      </c>
+      <c r="G144" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H144" s="10" t="s">
+        <v>382</v>
+      </c>
+      <c r="I144" s="8"/>
+    </row>
+    <row r="145" spans="1:9" ht="21">
+      <c r="A145" s="11"/>
+      <c r="B145" s="11"/>
+      <c r="C145" s="11"/>
+      <c r="D145" s="10"/>
+      <c r="E145" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F145" s="10">
+        <v>3</v>
+      </c>
+      <c r="G145" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H145" s="10" t="s">
+        <v>384</v>
+      </c>
+      <c r="I145" s="8"/>
+    </row>
+    <row r="146" spans="1:9" ht="21">
+      <c r="A146" s="11"/>
+      <c r="B146" s="11"/>
+      <c r="C146" s="11"/>
+      <c r="D146" s="9" t="s">
+        <v>385</v>
+      </c>
+      <c r="E146" s="10"/>
+      <c r="F146" s="9">
+        <v>7</v>
+      </c>
+      <c r="G146" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H146" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="I146" s="8"/>
+    </row>
+    <row r="147" spans="1:9" ht="21">
+      <c r="A147" s="11"/>
+      <c r="B147" s="11"/>
+      <c r="C147" s="11"/>
+      <c r="D147" s="10"/>
+      <c r="E147" s="10" t="s">
+        <v>387</v>
+      </c>
+      <c r="F147" s="10">
+        <v>2</v>
+      </c>
+      <c r="G147" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H147" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="I147" s="8"/>
+    </row>
+    <row r="148" spans="1:9" ht="21">
+      <c r="A148" s="11"/>
+      <c r="B148" s="11"/>
+      <c r="C148" s="11"/>
+      <c r="D148" s="10"/>
+      <c r="E148" s="10" t="s">
+        <v>388</v>
+      </c>
+      <c r="F148" s="10">
+        <v>3</v>
+      </c>
+      <c r="G148" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H148" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="I148" s="8"/>
+    </row>
+    <row r="149" spans="1:9" ht="21">
+      <c r="A149" s="11"/>
+      <c r="B149" s="11"/>
+      <c r="C149" s="11"/>
+      <c r="D149" s="10"/>
+      <c r="E149" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="F149" s="10">
+        <v>2</v>
+      </c>
+      <c r="G149" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H149" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="I149" s="8"/>
+    </row>
+    <row r="150" spans="1:9" ht="21">
+      <c r="A150" s="11"/>
+      <c r="B150" s="11"/>
+      <c r="C150" s="11"/>
+      <c r="D150" s="9" t="s">
+        <v>390</v>
+      </c>
+      <c r="E150" s="10"/>
+      <c r="F150" s="9">
+        <v>21</v>
+      </c>
+      <c r="G150" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H150" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="I150" s="8"/>
+    </row>
+    <row r="151" spans="1:9" ht="21">
+      <c r="A151" s="11"/>
+      <c r="B151" s="11"/>
+      <c r="C151" s="11"/>
+      <c r="D151" s="10"/>
+      <c r="E151" s="10" t="s">
+        <v>392</v>
+      </c>
+      <c r="F151" s="10">
+        <v>5</v>
+      </c>
+      <c r="G151" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H151" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="I151" s="8"/>
+    </row>
+    <row r="152" spans="1:9" ht="21">
+      <c r="A152" s="11"/>
+      <c r="B152" s="11"/>
+      <c r="C152" s="11"/>
+      <c r="D152" s="10"/>
+      <c r="E152" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="F152" s="10">
+        <v>3</v>
+      </c>
+      <c r="G152" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H152" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="I152" s="8"/>
+    </row>
+    <row r="153" spans="1:9" ht="21">
+      <c r="A153" s="11"/>
+      <c r="B153" s="11"/>
+      <c r="C153" s="11"/>
+      <c r="D153" s="10"/>
+      <c r="E153" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="F153" s="10">
+        <v>3</v>
+      </c>
+      <c r="G153" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H153" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="I153" s="8"/>
+    </row>
+    <row r="154" spans="1:9" ht="21">
+      <c r="A154" s="11"/>
+      <c r="B154" s="11"/>
+      <c r="C154" s="11"/>
+      <c r="D154" s="10"/>
+      <c r="E154" s="10" t="s">
+        <v>395</v>
+      </c>
+      <c r="F154" s="10">
+        <v>5</v>
+      </c>
+      <c r="G154" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H154" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="I154" s="8"/>
+    </row>
+    <row r="155" spans="1:9" ht="21">
+      <c r="A155" s="11"/>
+      <c r="B155" s="11"/>
+      <c r="C155" s="11"/>
+      <c r="D155" s="10"/>
+      <c r="E155" s="10" t="s">
+        <v>396</v>
+      </c>
+      <c r="F155" s="10">
+        <v>5</v>
+      </c>
+      <c r="G155" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H155" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="I155" s="8"/>
+    </row>
+    <row r="156" spans="1:9" ht="21">
+      <c r="A156" s="11"/>
+      <c r="B156" s="11"/>
+      <c r="C156" s="11"/>
+      <c r="D156" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="E156" s="10"/>
+      <c r="F156" s="9">
+        <v>23</v>
+      </c>
+      <c r="G156" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H156" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="I156" s="8"/>
+    </row>
+    <row r="157" spans="1:9" ht="21">
+      <c r="A157" s="11"/>
+      <c r="B157" s="11"/>
+      <c r="C157" s="11"/>
+      <c r="D157" s="10"/>
+      <c r="E157" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="F157" s="10">
+        <v>5</v>
+      </c>
+      <c r="G157" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H157" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="I157" s="8"/>
+    </row>
+    <row r="158" spans="1:9" ht="21">
+      <c r="A158" s="11"/>
+      <c r="B158" s="11"/>
+      <c r="C158" s="11"/>
+      <c r="D158" s="10"/>
+      <c r="E158" s="10" t="s">
+        <v>399</v>
+      </c>
+      <c r="F158" s="10">
+        <v>5</v>
+      </c>
+      <c r="G158" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H158" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="I158" s="8"/>
+    </row>
+    <row r="159" spans="1:9" ht="21">
+      <c r="A159" s="11"/>
+      <c r="B159" s="11"/>
+      <c r="C159" s="11"/>
+      <c r="D159" s="10"/>
+      <c r="E159" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="F159" s="10">
+        <v>8</v>
+      </c>
+      <c r="G159" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H159" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="I159" s="8"/>
+    </row>
+    <row r="160" spans="1:9" ht="21">
+      <c r="A160" s="11"/>
+      <c r="B160" s="11"/>
+      <c r="C160" s="11"/>
+      <c r="D160" s="10"/>
+      <c r="E160" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F160" s="10">
+        <v>3</v>
+      </c>
+      <c r="G160" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H160" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="I160" s="8"/>
+    </row>
+    <row r="161" spans="1:9" ht="21">
+      <c r="A161" s="11"/>
+      <c r="B161" s="11"/>
+      <c r="C161" s="11"/>
+      <c r="D161" s="10"/>
+      <c r="E161" s="10" t="s">
+        <v>402</v>
+      </c>
+      <c r="F161" s="10">
+        <v>2</v>
+      </c>
+      <c r="G161" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H161" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I161" s="8"/>
+    </row>
+    <row r="162" spans="1:9" ht="21">
+      <c r="A162" s="11"/>
+      <c r="B162" s="11"/>
+      <c r="C162" s="11"/>
+      <c r="D162" s="9" t="s">
+        <v>403</v>
+      </c>
+      <c r="E162" s="10"/>
+      <c r="F162" s="9">
+        <v>19</v>
+      </c>
+      <c r="G162" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H162" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="I162" s="8"/>
+    </row>
+    <row r="163" spans="1:9" ht="21">
+      <c r="A163" s="11"/>
+      <c r="B163" s="11"/>
+      <c r="C163" s="11"/>
+      <c r="D163" s="10"/>
+      <c r="E163" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="F163" s="10">
+        <v>5</v>
+      </c>
+      <c r="G163" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H163" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I163" s="8"/>
+    </row>
+    <row r="164" spans="1:9" ht="21">
+      <c r="A164" s="11"/>
+      <c r="B164" s="11"/>
+      <c r="C164" s="11"/>
+      <c r="D164" s="10"/>
+      <c r="E164" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="F164" s="10">
+        <v>3</v>
+      </c>
+      <c r="G164" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H164" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I164" s="8"/>
+    </row>
+    <row r="165" spans="1:9" ht="21">
+      <c r="A165" s="11"/>
+      <c r="B165" s="11"/>
+      <c r="C165" s="11"/>
+      <c r="D165" s="10"/>
+      <c r="E165" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="F165" s="10">
+        <v>3</v>
+      </c>
+      <c r="G165" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H165" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="I165" s="8"/>
+    </row>
+    <row r="166" spans="1:9" ht="21">
+      <c r="A166" s="11"/>
+      <c r="B166" s="11"/>
+      <c r="C166" s="11"/>
+      <c r="D166" s="10"/>
+      <c r="E166" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="F166" s="10">
+        <v>3</v>
+      </c>
+      <c r="G166" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H166" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I166" s="8"/>
+    </row>
+    <row r="167" spans="1:9" ht="21">
+      <c r="A167" s="11"/>
+      <c r="B167" s="11"/>
+      <c r="C167" s="11"/>
+      <c r="D167" s="10"/>
+      <c r="E167" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="F167" s="10">
+        <v>5</v>
+      </c>
+      <c r="G167" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H167" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I167" s="8"/>
+    </row>
+    <row r="168" spans="1:9" ht="21">
+      <c r="A168" s="11"/>
+      <c r="B168" s="11" t="s">
+        <v>432</v>
+      </c>
+      <c r="C168" s="11">
+        <v>34</v>
+      </c>
+      <c r="D168" s="9" t="s">
+        <v>409</v>
+      </c>
+      <c r="E168" s="10"/>
+      <c r="F168" s="9">
+        <v>16</v>
+      </c>
+      <c r="G168" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H168" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="I168" s="8"/>
+    </row>
+    <row r="169" spans="1:9" ht="21">
+      <c r="A169" s="11"/>
+      <c r="B169" s="11"/>
+      <c r="C169" s="11"/>
+      <c r="D169" s="10"/>
+      <c r="E169" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="F169" s="10">
+        <v>5</v>
+      </c>
+      <c r="G169" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H169" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="I169" s="8"/>
+    </row>
+    <row r="170" spans="1:9" ht="21">
+      <c r="A170" s="11"/>
+      <c r="B170" s="11"/>
+      <c r="C170" s="11"/>
+      <c r="D170" s="10"/>
+      <c r="E170" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="F170" s="10">
+        <v>3</v>
+      </c>
+      <c r="G170" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H170" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I170" s="8"/>
+    </row>
+    <row r="171" spans="1:9" ht="21">
+      <c r="A171" s="11"/>
+      <c r="B171" s="11"/>
+      <c r="C171" s="11"/>
+      <c r="D171" s="10"/>
+      <c r="E171" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="F171" s="10">
+        <v>3</v>
+      </c>
+      <c r="G171" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H171" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="I171" s="8"/>
+    </row>
+    <row r="172" spans="1:9" ht="21">
+      <c r="A172" s="11"/>
+      <c r="B172" s="11"/>
+      <c r="C172" s="11"/>
+      <c r="D172" s="10"/>
+      <c r="E172" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="F172" s="10">
+        <v>5</v>
+      </c>
+      <c r="G172" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H172" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="I172" s="8"/>
+    </row>
+    <row r="173" spans="1:9" ht="21">
+      <c r="A173" s="11"/>
+      <c r="B173" s="11"/>
+      <c r="C173" s="11"/>
+      <c r="D173" s="9" t="s">
+        <v>417</v>
+      </c>
+      <c r="E173" s="10"/>
+      <c r="F173" s="9">
+        <v>18</v>
+      </c>
+      <c r="G173" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H173" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I173" s="8"/>
+    </row>
+    <row r="174" spans="1:9" ht="21">
+      <c r="A174" s="11"/>
+      <c r="B174" s="11"/>
+      <c r="C174" s="11"/>
+      <c r="D174" s="10"/>
+      <c r="E174" s="10" t="s">
+        <v>418</v>
+      </c>
+      <c r="F174" s="10">
+        <v>5</v>
+      </c>
+      <c r="G174" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H174" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I174" s="8"/>
+    </row>
+    <row r="175" spans="1:9" ht="21">
+      <c r="A175" s="11"/>
+      <c r="B175" s="11"/>
+      <c r="C175" s="11"/>
+      <c r="D175" s="10"/>
+      <c r="E175" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="F175" s="10">
+        <v>5</v>
+      </c>
+      <c r="G175" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H175" s="10" t="s">
+        <v>356</v>
+      </c>
+      <c r="I175" s="8"/>
+    </row>
+    <row r="176" spans="1:9" ht="21">
+      <c r="A176" s="11"/>
+      <c r="B176" s="11"/>
+      <c r="C176" s="11"/>
+      <c r="D176" s="10"/>
+      <c r="E176" s="10" t="s">
+        <v>420</v>
+      </c>
+      <c r="F176" s="10">
+        <v>5</v>
+      </c>
+      <c r="G176" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H176" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="I176" s="8"/>
+    </row>
+    <row r="177" spans="1:9" ht="21">
+      <c r="A177" s="11"/>
+      <c r="B177" s="11"/>
+      <c r="C177" s="11"/>
+      <c r="D177" s="10"/>
+      <c r="E177" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F177" s="10">
+        <v>3</v>
+      </c>
+      <c r="G177" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H177" s="10" t="s">
+        <v>422</v>
+      </c>
+      <c r="I177" s="8"/>
+    </row>
+    <row r="178" spans="1:9" ht="21">
+      <c r="A178" s="11"/>
+      <c r="B178" s="11" t="s">
+        <v>436</v>
+      </c>
+      <c r="C178" s="12">
+        <v>26</v>
+      </c>
+      <c r="D178" s="9" t="s">
+        <v>423</v>
+      </c>
+      <c r="E178" s="10"/>
+      <c r="F178" s="9">
+        <v>26</v>
+      </c>
+      <c r="G178" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H178" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="I178" s="8" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9" ht="21">
+      <c r="A179" s="11"/>
+      <c r="B179" s="11"/>
+      <c r="C179" s="12"/>
+      <c r="D179" s="10"/>
+      <c r="E179" s="10" t="s">
+        <v>425</v>
+      </c>
+      <c r="F179" s="10">
+        <v>8</v>
+      </c>
+      <c r="G179" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H179" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="I179" s="8"/>
+    </row>
+    <row r="180" spans="1:9" ht="21">
+      <c r="A180" s="11"/>
+      <c r="B180" s="11"/>
+      <c r="C180" s="12"/>
+      <c r="D180" s="10"/>
+      <c r="E180" s="10" t="s">
+        <v>427</v>
+      </c>
+      <c r="F180" s="10">
+        <v>8</v>
+      </c>
+      <c r="G180" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H180" s="10" t="s">
+        <v>426</v>
+      </c>
+      <c r="I180" s="8"/>
+    </row>
+    <row r="181" spans="1:9" ht="21">
+      <c r="A181" s="11"/>
+      <c r="B181" s="11"/>
+      <c r="C181" s="12"/>
+      <c r="D181" s="10"/>
+      <c r="E181" s="10" t="s">
+        <v>428</v>
+      </c>
+      <c r="F181" s="10">
+        <v>5</v>
+      </c>
+      <c r="G181" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H181" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="I181" s="8"/>
+    </row>
+    <row r="182" spans="1:9" ht="21">
+      <c r="A182" s="11"/>
+      <c r="B182" s="11"/>
+      <c r="C182" s="12"/>
+      <c r="D182" s="10"/>
+      <c r="E182" s="10" t="s">
+        <v>430</v>
+      </c>
+      <c r="F182" s="10">
+        <v>5</v>
+      </c>
+      <c r="G182" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H182" s="10" t="s">
+        <v>429</v>
+      </c>
+      <c r="I182" s="8"/>
+    </row>
+    <row r="183" spans="1:9" ht="21">
+      <c r="A183" s="13" t="s">
+        <v>517</v>
+      </c>
+      <c r="B183" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="C183" s="13">
+        <v>35</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>440</v>
+      </c>
+      <c r="E183" s="10"/>
+      <c r="F183" s="10">
+        <v>19</v>
+      </c>
+      <c r="G183" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H183" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9" ht="21">
+      <c r="A184" s="13"/>
+      <c r="B184" s="13"/>
+      <c r="C184" s="13"/>
+      <c r="D184" s="10"/>
+      <c r="E184" s="10" t="s">
+        <v>441</v>
+      </c>
+      <c r="F184" s="10">
+        <v>5</v>
+      </c>
+      <c r="G184" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H184" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9" ht="21">
+      <c r="A185" s="13"/>
+      <c r="B185" s="13"/>
+      <c r="C185" s="13"/>
+      <c r="D185" s="10"/>
+      <c r="E185" s="10" t="s">
+        <v>442</v>
+      </c>
+      <c r="F185" s="10">
+        <v>3</v>
+      </c>
+      <c r="G185" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H185" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9" ht="21">
+      <c r="A186" s="13"/>
+      <c r="B186" s="13"/>
+      <c r="C186" s="13"/>
+      <c r="D186" s="10"/>
+      <c r="E186" s="10" t="s">
+        <v>443</v>
+      </c>
+      <c r="F186" s="10">
+        <v>5</v>
+      </c>
+      <c r="G186" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H186" s="10" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9" ht="21">
+      <c r="A187" s="13"/>
+      <c r="B187" s="13"/>
+      <c r="C187" s="13"/>
+      <c r="D187" s="10"/>
+      <c r="E187" s="10" t="s">
+        <v>444</v>
+      </c>
+      <c r="F187" s="10">
+        <v>3</v>
+      </c>
+      <c r="G187" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H187" s="10" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9" ht="21">
+      <c r="A188" s="13"/>
+      <c r="B188" s="13"/>
+      <c r="C188" s="13"/>
+      <c r="D188" s="10"/>
+      <c r="E188" s="10" t="s">
+        <v>446</v>
+      </c>
+      <c r="F188" s="10">
+        <v>3</v>
+      </c>
+      <c r="G188" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H188" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9" ht="21">
+      <c r="A189" s="13"/>
+      <c r="B189" s="13"/>
+      <c r="C189" s="13"/>
+      <c r="D189" s="10" t="s">
+        <v>447</v>
+      </c>
+      <c r="E189" s="10"/>
+      <c r="F189" s="10">
+        <v>16</v>
+      </c>
+      <c r="G189" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H189" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9" ht="21">
+      <c r="A190" s="13"/>
+      <c r="B190" s="13"/>
+      <c r="C190" s="13"/>
+      <c r="D190" s="10"/>
+      <c r="E190" s="10" t="s">
+        <v>448</v>
+      </c>
+      <c r="F190" s="10">
+        <v>3</v>
+      </c>
+      <c r="G190" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H190" s="10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9" ht="21">
+      <c r="A191" s="13"/>
+      <c r="B191" s="13"/>
+      <c r="C191" s="13"/>
+      <c r="D191" s="10"/>
+      <c r="E191" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="F191" s="10">
+        <v>2</v>
+      </c>
+      <c r="G191" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H191" s="10" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9" ht="21">
+      <c r="A192" s="13"/>
+      <c r="B192" s="13"/>
+      <c r="C192" s="13"/>
+      <c r="D192" s="10"/>
+      <c r="E192" s="10" t="s">
+        <v>452</v>
+      </c>
+      <c r="F192" s="10">
+        <v>3</v>
+      </c>
+      <c r="G192" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H192" s="10" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8" ht="21">
+      <c r="A193" s="13"/>
+      <c r="B193" s="13"/>
+      <c r="C193" s="13"/>
+      <c r="D193" s="10"/>
+      <c r="E193" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="F193" s="10">
+        <v>5</v>
+      </c>
+      <c r="G193" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H193" s="10" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="194" spans="1:8" ht="21">
+      <c r="A194" s="13"/>
+      <c r="B194" s="13"/>
+      <c r="C194" s="13"/>
+      <c r="D194" s="10"/>
+      <c r="E194" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="F194" s="10">
+        <v>3</v>
+      </c>
+      <c r="G194" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H194" s="10" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" ht="21">
+      <c r="A195" s="13"/>
+      <c r="B195" s="13" t="s">
+        <v>435</v>
+      </c>
+      <c r="C195" s="13">
+        <v>124</v>
+      </c>
+      <c r="D195" s="10" t="s">
+        <v>458</v>
+      </c>
+      <c r="E195" s="10"/>
+      <c r="F195" s="10">
+        <v>16</v>
+      </c>
+      <c r="G195" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H195" s="10" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="196" spans="1:8" ht="21">
+      <c r="A196" s="13"/>
+      <c r="B196" s="13"/>
+      <c r="C196" s="13"/>
+      <c r="D196" s="10"/>
+      <c r="E196" s="10" t="s">
+        <v>459</v>
+      </c>
+      <c r="F196" s="10">
+        <v>2</v>
+      </c>
+      <c r="G196" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H196" s="10" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="197" spans="1:8" ht="21">
+      <c r="A197" s="13"/>
+      <c r="B197" s="13"/>
+      <c r="C197" s="13"/>
+      <c r="D197" s="10"/>
+      <c r="E197" s="10" t="s">
+        <v>460</v>
+      </c>
+      <c r="F197" s="10">
+        <v>3</v>
+      </c>
+      <c r="G197" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H197" s="10" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8" ht="21">
+      <c r="A198" s="13"/>
+      <c r="B198" s="13"/>
+      <c r="C198" s="13"/>
+      <c r="D198" s="10"/>
+      <c r="E198" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F198" s="10">
+        <v>3</v>
+      </c>
+      <c r="G198" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H198" s="10" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="199" spans="1:8" ht="21">
+      <c r="A199" s="13"/>
+      <c r="B199" s="13"/>
+      <c r="C199" s="13"/>
+      <c r="D199" s="10"/>
+      <c r="E199" s="10" t="s">
+        <v>462</v>
+      </c>
+      <c r="F199" s="10">
+        <v>3</v>
+      </c>
+      <c r="G199" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H199" s="10" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8" ht="21">
+      <c r="A200" s="13"/>
+      <c r="B200" s="13"/>
+      <c r="C200" s="13"/>
+      <c r="D200" s="10"/>
+      <c r="E200" s="10" t="s">
+        <v>463</v>
+      </c>
+      <c r="F200" s="10">
+        <v>5</v>
+      </c>
+      <c r="G200" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H200" s="10" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="201" spans="1:8" ht="21">
+      <c r="A201" s="13"/>
+      <c r="B201" s="13"/>
+      <c r="C201" s="13"/>
+      <c r="D201" s="10" t="s">
+        <v>464</v>
+      </c>
+      <c r="E201" s="10"/>
+      <c r="F201" s="10">
+        <v>17</v>
+      </c>
+      <c r="G201" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H201" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="202" spans="1:8" ht="21">
+      <c r="A202" s="13"/>
+      <c r="B202" s="13"/>
+      <c r="C202" s="13"/>
+      <c r="D202" s="10"/>
+      <c r="E202" s="10" t="s">
+        <v>465</v>
+      </c>
+      <c r="F202" s="10">
+        <v>3</v>
+      </c>
+      <c r="G202" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H202" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="203" spans="1:8" ht="21">
+      <c r="A203" s="13"/>
+      <c r="B203" s="13"/>
+      <c r="C203" s="13"/>
+      <c r="D203" s="10"/>
+      <c r="E203" s="10" t="s">
+        <v>466</v>
+      </c>
+      <c r="F203" s="10">
+        <v>5</v>
+      </c>
+      <c r="G203" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H203" s="10" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8" ht="21">
+      <c r="A204" s="13"/>
+      <c r="B204" s="13"/>
+      <c r="C204" s="13"/>
+      <c r="D204" s="10"/>
+      <c r="E204" s="10" t="s">
+        <v>467</v>
+      </c>
+      <c r="F204" s="10">
+        <v>3</v>
+      </c>
+      <c r="G204" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H204" s="10" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="205" spans="1:8" ht="21">
+      <c r="A205" s="13"/>
+      <c r="B205" s="13"/>
+      <c r="C205" s="13"/>
+      <c r="D205" s="10"/>
+      <c r="E205" s="10" t="s">
+        <v>468</v>
+      </c>
+      <c r="F205" s="10">
+        <v>3</v>
+      </c>
+      <c r="G205" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H205" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="206" spans="1:8" ht="21">
+      <c r="A206" s="13"/>
+      <c r="B206" s="13"/>
+      <c r="C206" s="13"/>
+      <c r="D206" s="10"/>
+      <c r="E206" s="10" t="s">
+        <v>469</v>
+      </c>
+      <c r="F206" s="10">
+        <v>3</v>
+      </c>
+      <c r="G206" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H206" s="10" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="207" spans="1:8" ht="21">
+      <c r="A207" s="13"/>
+      <c r="B207" s="13"/>
+      <c r="C207" s="13"/>
+      <c r="D207" s="10" t="s">
+        <v>470</v>
+      </c>
+      <c r="E207" s="10"/>
+      <c r="F207" s="10">
+        <v>23</v>
+      </c>
+      <c r="G207" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H207" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="208" spans="1:8" ht="21">
+      <c r="A208" s="13"/>
+      <c r="B208" s="13"/>
+      <c r="C208" s="13"/>
+      <c r="D208" s="10"/>
+      <c r="E208" s="10" t="s">
+        <v>471</v>
+      </c>
+      <c r="F208" s="10">
+        <v>5</v>
+      </c>
+      <c r="G208" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H208" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="209" spans="1:8" ht="21">
+      <c r="A209" s="13"/>
+      <c r="B209" s="13"/>
+      <c r="C209" s="13"/>
+      <c r="D209" s="10"/>
+      <c r="E209" s="10" t="s">
+        <v>472</v>
+      </c>
+      <c r="F209" s="10">
+        <v>5</v>
+      </c>
+      <c r="G209" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H209" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8" ht="21">
+      <c r="A210" s="13"/>
+      <c r="B210" s="13"/>
+      <c r="C210" s="13"/>
+      <c r="D210" s="10"/>
+      <c r="E210" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F210" s="10">
+        <v>5</v>
+      </c>
+      <c r="G210" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H210" s="10" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="211" spans="1:8" ht="21">
+      <c r="A211" s="13"/>
+      <c r="B211" s="13"/>
+      <c r="C211" s="13"/>
+      <c r="D211" s="10"/>
+      <c r="E211" s="10" t="s">
+        <v>474</v>
+      </c>
+      <c r="F211" s="10">
+        <v>3</v>
+      </c>
+      <c r="G211" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H211" s="10" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="212" spans="1:8" ht="21">
+      <c r="A212" s="13"/>
+      <c r="B212" s="13"/>
+      <c r="C212" s="13"/>
+      <c r="D212" s="10"/>
+      <c r="E212" s="10" t="s">
+        <v>475</v>
+      </c>
+      <c r="F212" s="10">
+        <v>5</v>
+      </c>
+      <c r="G212" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H212" s="10" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="213" spans="1:8" ht="21">
+      <c r="A213" s="13"/>
+      <c r="B213" s="13"/>
+      <c r="C213" s="13"/>
+      <c r="D213" s="10" t="s">
+        <v>477</v>
+      </c>
+      <c r="E213" s="10"/>
+      <c r="F213" s="10">
+        <v>13</v>
+      </c>
+      <c r="G213" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H213" s="10" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="214" spans="1:8" ht="21">
+      <c r="A214" s="13"/>
+      <c r="B214" s="13"/>
+      <c r="C214" s="13"/>
+      <c r="D214" s="10"/>
+      <c r="E214" s="10" t="s">
+        <v>479</v>
+      </c>
+      <c r="F214" s="10">
+        <v>2</v>
+      </c>
+      <c r="G214" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H214" s="10" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="215" spans="1:8" ht="21">
+      <c r="A215" s="13"/>
+      <c r="B215" s="13"/>
+      <c r="C215" s="13"/>
+      <c r="D215" s="10"/>
+      <c r="E215" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="F215" s="10">
+        <v>5</v>
+      </c>
+      <c r="G215" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H215" s="10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8" ht="21">
+      <c r="A216" s="13"/>
+      <c r="B216" s="13"/>
+      <c r="C216" s="13"/>
+      <c r="D216" s="10"/>
+      <c r="E216" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="F216" s="10">
+        <v>3</v>
+      </c>
+      <c r="G216" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H216" s="10" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="217" spans="1:8" ht="21">
+      <c r="A217" s="13"/>
+      <c r="B217" s="13"/>
+      <c r="C217" s="13"/>
+      <c r="D217" s="10"/>
+      <c r="E217" s="10" t="s">
+        <v>484</v>
+      </c>
+      <c r="F217" s="10">
+        <v>3</v>
+      </c>
+      <c r="G217" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H217" s="10" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="218" spans="1:8" ht="21">
+      <c r="A218" s="13"/>
+      <c r="B218" s="13"/>
+      <c r="C218" s="13"/>
+      <c r="D218" s="10" t="s">
+        <v>486</v>
+      </c>
+      <c r="E218" s="10"/>
+      <c r="F218" s="10">
+        <v>24</v>
+      </c>
+      <c r="G218" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H218" s="10" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8" ht="21">
+      <c r="A219" s="13"/>
+      <c r="B219" s="13"/>
+      <c r="C219" s="13"/>
+      <c r="D219" s="10"/>
+      <c r="E219" s="10" t="s">
+        <v>487</v>
+      </c>
+      <c r="F219" s="10">
+        <v>5</v>
+      </c>
+      <c r="G219" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H219" s="10" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="220" spans="1:8" ht="21">
+      <c r="A220" s="13"/>
+      <c r="B220" s="13"/>
+      <c r="C220" s="13"/>
+      <c r="D220" s="10"/>
+      <c r="E220" s="10" t="s">
+        <v>488</v>
+      </c>
+      <c r="F220" s="10">
+        <v>3</v>
+      </c>
+      <c r="G220" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H220" s="10" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="221" spans="1:8" ht="21">
+      <c r="A221" s="13"/>
+      <c r="B221" s="13"/>
+      <c r="C221" s="13"/>
+      <c r="D221" s="10"/>
+      <c r="E221" s="10" t="s">
+        <v>490</v>
+      </c>
+      <c r="F221" s="10">
+        <v>5</v>
+      </c>
+      <c r="G221" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H221" s="10" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="222" spans="1:8" ht="21">
+      <c r="A222" s="13"/>
+      <c r="B222" s="13"/>
+      <c r="C222" s="13"/>
+      <c r="D222" s="10"/>
+      <c r="E222" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="F222" s="10">
+        <v>5</v>
+      </c>
+      <c r="G222" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H222" s="10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="223" spans="1:8" ht="21">
+      <c r="A223" s="13"/>
+      <c r="B223" s="13"/>
+      <c r="C223" s="13"/>
+      <c r="D223" s="10"/>
+      <c r="E223" s="10" t="s">
+        <v>494</v>
+      </c>
+      <c r="F223" s="10">
+        <v>3</v>
+      </c>
+      <c r="G223" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H223" s="10" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="224" spans="1:8" ht="21">
+      <c r="A224" s="13"/>
+      <c r="B224" s="13"/>
+      <c r="C224" s="13"/>
+      <c r="D224" s="10"/>
+      <c r="E224" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="F224" s="10">
+        <v>3</v>
+      </c>
+      <c r="G224" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H224" s="10" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="21">
+      <c r="A225" s="13"/>
+      <c r="B225" s="13"/>
+      <c r="C225" s="13"/>
+      <c r="D225" s="10" t="s">
+        <v>498</v>
+      </c>
+      <c r="E225" s="10"/>
+      <c r="F225" s="10">
+        <v>19</v>
+      </c>
+      <c r="G225" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H225" s="10" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="226" spans="1:8" ht="21">
+      <c r="A226" s="13"/>
+      <c r="B226" s="13"/>
+      <c r="C226" s="13"/>
+      <c r="D226" s="10"/>
+      <c r="E226" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="F226" s="10">
+        <v>3</v>
+      </c>
+      <c r="G226" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H226" s="10" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" ht="21">
+      <c r="A227" s="13"/>
+      <c r="B227" s="13"/>
+      <c r="C227" s="13"/>
+      <c r="D227" s="10"/>
+      <c r="E227" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="F227" s="10">
+        <v>3</v>
+      </c>
+      <c r="G227" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H227" s="10" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8" ht="21">
+      <c r="A228" s="13"/>
+      <c r="B228" s="13"/>
+      <c r="C228" s="13"/>
+      <c r="D228" s="10"/>
+      <c r="E228" s="10" t="s">
+        <v>502</v>
+      </c>
+      <c r="F228" s="10">
+        <v>3</v>
+      </c>
+      <c r="G228" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H228" s="10" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="229" spans="1:8" ht="21">
+      <c r="A229" s="13"/>
+      <c r="B229" s="13"/>
+      <c r="C229" s="13"/>
+      <c r="D229" s="10"/>
+      <c r="E229" s="10" t="s">
+        <v>504</v>
+      </c>
+      <c r="F229" s="10">
+        <v>3</v>
+      </c>
+      <c r="G229" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H229" s="10" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" ht="21">
+      <c r="A230" s="13"/>
+      <c r="B230" s="13"/>
+      <c r="C230" s="13"/>
+      <c r="D230" s="10"/>
+      <c r="E230" s="10" t="s">
+        <v>506</v>
+      </c>
+      <c r="F230" s="10">
+        <v>5</v>
+      </c>
+      <c r="G230" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H230" s="10" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" ht="21">
+      <c r="A231" s="13"/>
+      <c r="B231" s="13"/>
+      <c r="C231" s="13"/>
+      <c r="D231" s="10"/>
+      <c r="E231" s="10" t="s">
+        <v>508</v>
+      </c>
+      <c r="F231" s="10">
+        <v>2</v>
+      </c>
+      <c r="G231" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H231" s="10" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" ht="21">
+      <c r="A232" s="13"/>
+      <c r="B232" s="13"/>
+      <c r="C232" s="13"/>
+      <c r="D232" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="E232" s="10"/>
+      <c r="F232" s="10">
+        <v>12</v>
+      </c>
+      <c r="G232" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H232" s="10" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" ht="21">
+      <c r="A233" s="13"/>
+      <c r="B233" s="13"/>
+      <c r="C233" s="13"/>
+      <c r="D233" s="10"/>
+      <c r="E233" s="10" t="s">
+        <v>511</v>
+      </c>
+      <c r="F233" s="10">
+        <v>3</v>
+      </c>
+      <c r="G233" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H233" s="10" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" ht="21">
+      <c r="A234" s="13"/>
+      <c r="B234" s="13"/>
+      <c r="C234" s="13"/>
+      <c r="D234" s="10"/>
+      <c r="E234" s="10" t="s">
+        <v>513</v>
+      </c>
+      <c r="F234" s="10">
+        <v>3</v>
+      </c>
+      <c r="G234" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H234" s="10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" ht="21">
+      <c r="A235" s="13"/>
+      <c r="B235" s="13"/>
+      <c r="C235" s="13"/>
+      <c r="D235" s="10"/>
+      <c r="E235" s="10" t="s">
+        <v>514</v>
+      </c>
+      <c r="F235" s="10">
+        <v>3</v>
+      </c>
+      <c r="G235" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H235" s="10" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" ht="21">
+      <c r="A236" s="13"/>
+      <c r="B236" s="13"/>
+      <c r="C236" s="13"/>
+      <c r="D236" s="10"/>
+      <c r="E236" s="10" t="s">
+        <v>515</v>
+      </c>
+      <c r="F236" s="10">
+        <v>3</v>
+      </c>
+      <c r="G236" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H236" s="10" t="s">
+        <v>516</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:I182" xr:uid="{850196EF-B3FB-4345-AB35-B6DAC38626B4}"/>
+  <mergeCells count="28">
+    <mergeCell ref="C124:C167"/>
+    <mergeCell ref="A183:A236"/>
+    <mergeCell ref="B183:B194"/>
+    <mergeCell ref="B195:B236"/>
+    <mergeCell ref="C195:C236"/>
+    <mergeCell ref="C183:C194"/>
+    <mergeCell ref="C62:C84"/>
+    <mergeCell ref="C85:C92"/>
+    <mergeCell ref="C93:C104"/>
+    <mergeCell ref="C105:C123"/>
+    <mergeCell ref="A124:A182"/>
+    <mergeCell ref="B124:B167"/>
+    <mergeCell ref="B168:B177"/>
+    <mergeCell ref="B178:B182"/>
+    <mergeCell ref="C178:C182"/>
+    <mergeCell ref="C168:C177"/>
+    <mergeCell ref="A62:A92"/>
+    <mergeCell ref="B62:B84"/>
+    <mergeCell ref="B85:B92"/>
+    <mergeCell ref="A93:A123"/>
+    <mergeCell ref="B93:B104"/>
+    <mergeCell ref="B105:B123"/>
+    <mergeCell ref="A2:A33"/>
+    <mergeCell ref="B2:B33"/>
+    <mergeCell ref="C2:C33"/>
+    <mergeCell ref="A34:A61"/>
+    <mergeCell ref="B34:B61"/>
+    <mergeCell ref="C34:C61"/>
+  </mergeCells>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/docs/功能归属表.xlsx
+++ b/docs/功能归属表.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kaizhou/SynologyDrive/works/fxn-wms/docs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82639C7B-2541-1C47-B75A-E4B6B806D844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73579BC8-A119-194D-BD67-F7FCCE80AC7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="700" yWindow="800" windowWidth="32580" windowHeight="18720" activeTab="1" xr2:uid="{83DC34A4-855E-F341-94CD-123EDADA1840}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$I$182</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$I$270</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1234" uniqueCount="518">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1338" uniqueCount="561">
   <si>
     <t>功能模块</t>
   </si>
@@ -1610,6 +1610,135 @@
   <si>
     <t>SMT 发料</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>E1: 物料分类与路由决策</t>
+  </si>
+  <si>
+    <t>E6</t>
+  </si>
+  <si>
+    <t>US-E1-01: 物料类型识别</t>
+  </si>
+  <si>
+    <t>US-E1-02: 路由规则引擎实现</t>
+  </si>
+  <si>
+    <t>E6-02</t>
+  </si>
+  <si>
+    <t>US-E1-03: 路由决策 API</t>
+  </si>
+  <si>
+    <t>US-E1-02</t>
+  </si>
+  <si>
+    <t>US-E1-04: 物料属性扩展</t>
+  </si>
+  <si>
+    <t>E2: 特殊物料类型处理流程</t>
+  </si>
+  <si>
+    <t>E1, E6</t>
+  </si>
+  <si>
+    <t>US-E2-01: 高价值物料流程</t>
+  </si>
+  <si>
+    <t>US-E2-02: MSD物料流程</t>
+  </si>
+  <si>
+    <t>US-E2-03: 异形物料流程</t>
+  </si>
+  <si>
+    <t>US-E2-04: PCB物料流程</t>
+  </si>
+  <si>
+    <t>US-E2-05: 机构件物料流程</t>
+  </si>
+  <si>
+    <t>US-E2-06: QMS Webhook 集成</t>
+  </si>
+  <si>
+    <t>E3: 库位分配与上架执行</t>
+  </si>
+  <si>
+    <t>US-E3-01: 库位分配策略引擎</t>
+  </si>
+  <si>
+    <t>US-E3-02: RCS上架任务创建</t>
+  </si>
+  <si>
+    <t>US-E3-01</t>
+  </si>
+  <si>
+    <t>US-E3-03: 上架确认处理</t>
+  </si>
+  <si>
+    <t>US-E3-02</t>
+  </si>
+  <si>
+    <t>US-E3-04: 库位容量管理</t>
+  </si>
+  <si>
+    <t>E4: 异常处理与状态监控</t>
+  </si>
+  <si>
+    <t>US-E4-01: 异常检测与告警</t>
+  </si>
+  <si>
+    <t>US-E4-02: 人工介入工作流</t>
+  </si>
+  <si>
+    <t>US-E4-01</t>
+  </si>
+  <si>
+    <t>US-E4-03: RCS状态同步</t>
+  </si>
+  <si>
+    <t>E5: 报表与追溯</t>
+  </si>
+  <si>
+    <t>US-E5-01: 特殊物料移动报表</t>
+  </si>
+  <si>
+    <t>US-E5-02: 物料追溯查询</t>
+  </si>
+  <si>
+    <t>US-E5-03: 性能指标仪表板</t>
+  </si>
+  <si>
+    <t>US-E5-01</t>
+  </si>
+  <si>
+    <t>E6: 数据库架构与集成</t>
+  </si>
+  <si>
+    <t>US-E6-01: material_extension 表创建</t>
+  </si>
+  <si>
+    <t>US-E6-02: routing_rule 表创建</t>
+  </si>
+  <si>
+    <t>US-E6-03: special_material_log 表创建</t>
+  </si>
+  <si>
+    <t>US-E6-04: SAP物料属性批量同步</t>
+  </si>
+  <si>
+    <t>US-E6-01</t>
+  </si>
+  <si>
+    <t>E7: UI/PDA 功能增强</t>
+  </si>
+  <si>
+    <t>US-E7-01: 物料分类管理界面</t>
+  </si>
+  <si>
+    <t>US-E7-02: PDA特殊物料处理界面</t>
+  </si>
+  <si>
+    <t>US-E7-03: 异常处理仪表板</t>
   </si>
 </sst>
 </file>
@@ -3838,7 +3967,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{850196EF-B3FB-4345-AB35-B6DAC38626B4}">
-  <dimension ref="A1:I236"/>
+  <dimension ref="A1:I270"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <cols>
     <col min="1" max="1" width="26.83203125" bestFit="1" customWidth="1"/>
@@ -4977,7 +5106,7 @@
         <v>435</v>
       </c>
       <c r="C62" s="11">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D62" s="9" t="s">
         <v>282</v>
@@ -5344,7 +5473,7 @@
       </c>
       <c r="E82" s="10"/>
       <c r="F82" s="9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G82" s="10" t="s">
         <v>234</v>
@@ -5395,7 +5524,7 @@
         <v>435</v>
       </c>
       <c r="C85" s="11">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D85" s="9" t="s">
         <v>282</v>
@@ -8243,9 +8372,630 @@
         <v>516</v>
       </c>
     </row>
+    <row r="237" spans="1:8" ht="21">
+      <c r="A237" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="B237" s="13" t="s">
+        <v>432</v>
+      </c>
+      <c r="C237" s="13">
+        <v>113</v>
+      </c>
+      <c r="D237" s="10" t="s">
+        <v>518</v>
+      </c>
+      <c r="E237" s="10"/>
+      <c r="F237" s="10">
+        <v>14</v>
+      </c>
+      <c r="G237" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H237" s="10" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" ht="21">
+      <c r="A238" s="13"/>
+      <c r="B238" s="13"/>
+      <c r="C238" s="13"/>
+      <c r="D238" s="10"/>
+      <c r="E238" s="10" t="s">
+        <v>520</v>
+      </c>
+      <c r="F238" s="10">
+        <v>3</v>
+      </c>
+      <c r="G238" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H238" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" ht="21">
+      <c r="A239" s="13"/>
+      <c r="B239" s="13"/>
+      <c r="C239" s="13"/>
+      <c r="D239" s="10"/>
+      <c r="E239" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="F239" s="10">
+        <v>5</v>
+      </c>
+      <c r="G239" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H239" s="10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" ht="21">
+      <c r="A240" s="13"/>
+      <c r="B240" s="13"/>
+      <c r="C240" s="13"/>
+      <c r="D240" s="10"/>
+      <c r="E240" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="F240" s="10">
+        <v>3</v>
+      </c>
+      <c r="G240" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H240" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" ht="21">
+      <c r="A241" s="13"/>
+      <c r="B241" s="13"/>
+      <c r="C241" s="13"/>
+      <c r="D241" s="10"/>
+      <c r="E241" s="10" t="s">
+        <v>525</v>
+      </c>
+      <c r="F241" s="10">
+        <v>3</v>
+      </c>
+      <c r="G241" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H241" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" ht="21">
+      <c r="A242" s="13"/>
+      <c r="B242" s="13"/>
+      <c r="C242" s="13"/>
+      <c r="D242" s="10" t="s">
+        <v>526</v>
+      </c>
+      <c r="E242" s="10"/>
+      <c r="F242" s="10">
+        <v>34</v>
+      </c>
+      <c r="G242" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H242" s="10" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" ht="21">
+      <c r="A243" s="13"/>
+      <c r="B243" s="13"/>
+      <c r="C243" s="13"/>
+      <c r="D243" s="10"/>
+      <c r="E243" s="10" t="s">
+        <v>528</v>
+      </c>
+      <c r="F243" s="10">
+        <v>8</v>
+      </c>
+      <c r="G243" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H243" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" ht="21">
+      <c r="A244" s="13"/>
+      <c r="B244" s="13"/>
+      <c r="C244" s="13"/>
+      <c r="D244" s="10"/>
+      <c r="E244" s="10" t="s">
+        <v>529</v>
+      </c>
+      <c r="F244" s="10">
+        <v>8</v>
+      </c>
+      <c r="G244" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H244" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" ht="21">
+      <c r="A245" s="13"/>
+      <c r="B245" s="13"/>
+      <c r="C245" s="13"/>
+      <c r="D245" s="10"/>
+      <c r="E245" s="10" t="s">
+        <v>530</v>
+      </c>
+      <c r="F245" s="10">
+        <v>5</v>
+      </c>
+      <c r="G245" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H245" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" ht="21">
+      <c r="A246" s="13"/>
+      <c r="B246" s="13"/>
+      <c r="C246" s="13"/>
+      <c r="D246" s="10"/>
+      <c r="E246" s="10" t="s">
+        <v>531</v>
+      </c>
+      <c r="F246" s="10">
+        <v>5</v>
+      </c>
+      <c r="G246" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H246" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" ht="21">
+      <c r="A247" s="13"/>
+      <c r="B247" s="13"/>
+      <c r="C247" s="13"/>
+      <c r="D247" s="10"/>
+      <c r="E247" s="10" t="s">
+        <v>532</v>
+      </c>
+      <c r="F247" s="10">
+        <v>5</v>
+      </c>
+      <c r="G247" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H247" s="10" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" ht="21">
+      <c r="A248" s="13"/>
+      <c r="B248" s="13"/>
+      <c r="C248" s="13"/>
+      <c r="D248" s="10"/>
+      <c r="E248" s="10" t="s">
+        <v>533</v>
+      </c>
+      <c r="F248" s="10">
+        <v>3</v>
+      </c>
+      <c r="G248" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H248" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" ht="21">
+      <c r="A249" s="13"/>
+      <c r="B249" s="13"/>
+      <c r="C249" s="13"/>
+      <c r="D249" s="10" t="s">
+        <v>534</v>
+      </c>
+      <c r="E249" s="10"/>
+      <c r="F249" s="10">
+        <v>21</v>
+      </c>
+      <c r="G249" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H249" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" ht="21">
+      <c r="A250" s="13"/>
+      <c r="B250" s="13"/>
+      <c r="C250" s="13"/>
+      <c r="D250" s="10"/>
+      <c r="E250" s="10" t="s">
+        <v>535</v>
+      </c>
+      <c r="F250" s="10">
+        <v>8</v>
+      </c>
+      <c r="G250" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H250" s="10" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" ht="21">
+      <c r="A251" s="13"/>
+      <c r="B251" s="13"/>
+      <c r="C251" s="13"/>
+      <c r="D251" s="10"/>
+      <c r="E251" s="10" t="s">
+        <v>536</v>
+      </c>
+      <c r="F251" s="10">
+        <v>5</v>
+      </c>
+      <c r="G251" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H251" s="10" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" ht="21">
+      <c r="A252" s="13"/>
+      <c r="B252" s="13"/>
+      <c r="C252" s="13"/>
+      <c r="D252" s="10"/>
+      <c r="E252" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F252" s="10">
+        <v>5</v>
+      </c>
+      <c r="G252" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H252" s="10" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" ht="21">
+      <c r="A253" s="13"/>
+      <c r="B253" s="13"/>
+      <c r="C253" s="13"/>
+      <c r="D253" s="10"/>
+      <c r="E253" s="10" t="s">
+        <v>540</v>
+      </c>
+      <c r="F253" s="10">
+        <v>3</v>
+      </c>
+      <c r="G253" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H253" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" ht="21">
+      <c r="A254" s="13"/>
+      <c r="B254" s="13"/>
+      <c r="C254" s="13"/>
+      <c r="D254" s="10" t="s">
+        <v>541</v>
+      </c>
+      <c r="E254" s="10"/>
+      <c r="F254" s="10">
+        <v>13</v>
+      </c>
+      <c r="G254" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H254" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" ht="21">
+      <c r="A255" s="13"/>
+      <c r="B255" s="13"/>
+      <c r="C255" s="13"/>
+      <c r="D255" s="10"/>
+      <c r="E255" s="10" t="s">
+        <v>542</v>
+      </c>
+      <c r="F255" s="10">
+        <v>5</v>
+      </c>
+      <c r="G255" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H255" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" ht="21">
+      <c r="A256" s="13"/>
+      <c r="B256" s="13"/>
+      <c r="C256" s="13"/>
+      <c r="D256" s="10"/>
+      <c r="E256" s="10" t="s">
+        <v>543</v>
+      </c>
+      <c r="F256" s="10">
+        <v>5</v>
+      </c>
+      <c r="G256" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H256" s="10" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" ht="21">
+      <c r="A257" s="13"/>
+      <c r="B257" s="13"/>
+      <c r="C257" s="13"/>
+      <c r="D257" s="10"/>
+      <c r="E257" s="10" t="s">
+        <v>545</v>
+      </c>
+      <c r="F257" s="10">
+        <v>3</v>
+      </c>
+      <c r="G257" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H257" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" ht="21">
+      <c r="A258" s="13"/>
+      <c r="B258" s="13"/>
+      <c r="C258" s="13"/>
+      <c r="D258" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="E258" s="10"/>
+      <c r="F258" s="10">
+        <v>8</v>
+      </c>
+      <c r="G258" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H258" s="10" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" ht="21">
+      <c r="A259" s="13"/>
+      <c r="B259" s="13"/>
+      <c r="C259" s="13"/>
+      <c r="D259" s="10"/>
+      <c r="E259" s="10" t="s">
+        <v>547</v>
+      </c>
+      <c r="F259" s="10">
+        <v>3</v>
+      </c>
+      <c r="G259" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H259" s="10" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" ht="21">
+      <c r="A260" s="13"/>
+      <c r="B260" s="13"/>
+      <c r="C260" s="13"/>
+      <c r="D260" s="10"/>
+      <c r="E260" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="F260" s="10">
+        <v>3</v>
+      </c>
+      <c r="G260" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H260" s="10" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" ht="21">
+      <c r="A261" s="13"/>
+      <c r="B261" s="13"/>
+      <c r="C261" s="13"/>
+      <c r="D261" s="10"/>
+      <c r="E261" s="10" t="s">
+        <v>549</v>
+      </c>
+      <c r="F261" s="10">
+        <v>2</v>
+      </c>
+      <c r="G261" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H261" s="10" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" ht="21">
+      <c r="A262" s="13"/>
+      <c r="B262" s="13"/>
+      <c r="C262" s="13"/>
+      <c r="D262" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="E262" s="10"/>
+      <c r="F262" s="10">
+        <v>13</v>
+      </c>
+      <c r="G262" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H262" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" ht="21">
+      <c r="A263" s="13"/>
+      <c r="B263" s="13"/>
+      <c r="C263" s="13"/>
+      <c r="D263" s="10"/>
+      <c r="E263" s="10" t="s">
+        <v>552</v>
+      </c>
+      <c r="F263" s="10">
+        <v>3</v>
+      </c>
+      <c r="G263" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H263" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" ht="21">
+      <c r="A264" s="13"/>
+      <c r="B264" s="13"/>
+      <c r="C264" s="13"/>
+      <c r="D264" s="10"/>
+      <c r="E264" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="F264" s="10">
+        <v>3</v>
+      </c>
+      <c r="G264" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H264" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" ht="21">
+      <c r="A265" s="13"/>
+      <c r="B265" s="13"/>
+      <c r="C265" s="13"/>
+      <c r="D265" s="10"/>
+      <c r="E265" s="10" t="s">
+        <v>554</v>
+      </c>
+      <c r="F265" s="10">
+        <v>2</v>
+      </c>
+      <c r="G265" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H265" s="10" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" ht="21">
+      <c r="A266" s="13"/>
+      <c r="B266" s="13"/>
+      <c r="C266" s="13"/>
+      <c r="D266" s="10"/>
+      <c r="E266" s="10" t="s">
+        <v>555</v>
+      </c>
+      <c r="F266" s="10">
+        <v>5</v>
+      </c>
+      <c r="G266" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="H266" s="10" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" ht="21">
+      <c r="A267" s="13"/>
+      <c r="B267" s="13"/>
+      <c r="C267" s="13"/>
+      <c r="D267" s="10" t="s">
+        <v>557</v>
+      </c>
+      <c r="E267" s="10"/>
+      <c r="F267" s="10">
+        <v>10</v>
+      </c>
+      <c r="G267" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H267" s="10" t="s">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" ht="21">
+      <c r="A268" s="13"/>
+      <c r="B268" s="13"/>
+      <c r="C268" s="13"/>
+      <c r="D268" s="10"/>
+      <c r="E268" s="10" t="s">
+        <v>558</v>
+      </c>
+      <c r="F268" s="10">
+        <v>5</v>
+      </c>
+      <c r="G268" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H268" s="10" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="269" spans="1:8" ht="21">
+      <c r="A269" s="13"/>
+      <c r="B269" s="13"/>
+      <c r="C269" s="13"/>
+      <c r="D269" s="10"/>
+      <c r="E269" s="10" t="s">
+        <v>559</v>
+      </c>
+      <c r="F269" s="10">
+        <v>3</v>
+      </c>
+      <c r="G269" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H269" s="10" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="270" spans="1:8" ht="21">
+      <c r="A270" s="13"/>
+      <c r="B270" s="13"/>
+      <c r="C270" s="13"/>
+      <c r="D270" s="10"/>
+      <c r="E270" s="10" t="s">
+        <v>560</v>
+      </c>
+      <c r="F270" s="10">
+        <v>2</v>
+      </c>
+      <c r="G270" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="H270" s="10" t="s">
+        <v>221</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:I182" xr:uid="{850196EF-B3FB-4345-AB35-B6DAC38626B4}"/>
-  <mergeCells count="28">
+  <autoFilter ref="A1:I270" xr:uid="{850196EF-B3FB-4345-AB35-B6DAC38626B4}"/>
+  <mergeCells count="31">
+    <mergeCell ref="A237:A270"/>
+    <mergeCell ref="B237:B270"/>
+    <mergeCell ref="C237:C270"/>
     <mergeCell ref="C124:C167"/>
     <mergeCell ref="A183:A236"/>
     <mergeCell ref="B183:B194"/>
@@ -8277,5 +9027,6 @@
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>